--- a/research/traditional_assets/database/data/austria/austria_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_oil_gas_integrated.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09127054477181051</v>
+        <v>0.09108569546435817</v>
       </c>
       <c r="C2">
-        <v>22142.34140705129</v>
+        <v>21935.36039344208</v>
       </c>
       <c r="D2">
-        <v>15680.14140705129</v>
+        <v>15702.94639344208</v>
       </c>
       <c r="E2">
-        <v>-10329</v>
+        <v>-10099.214</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>229.786</v>
       </c>
       <c r="G2">
         <v>6462.2</v>
@@ -1457,28 +1457,28 @@
         <v>4301.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>11.5582358</v>
       </c>
       <c r="N2">
-        <v>4301.8</v>
+        <v>4290.2417642</v>
       </c>
       <c r="O2">
-        <v>1032.432</v>
+        <v>1029.658023408</v>
       </c>
       <c r="P2">
-        <v>3269.368</v>
+        <v>3260.583740792</v>
       </c>
       <c r="Q2">
-        <v>6159.168000000001</v>
+        <v>6150.383740792</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09127054477181051</v>
+        <v>0.09161961158015977</v>
       </c>
       <c r="T2">
-        <v>0.9349222590860211</v>
+        <v>0.9420994400648633</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>372.1848277225837</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09108569546435817</v>
+        <v>0.09090084615690582</v>
       </c>
       <c r="C3">
-        <v>21935.36039344208</v>
+        <v>21728.4458109793</v>
       </c>
       <c r="D3">
-        <v>15702.94639344208</v>
+        <v>15725.8178109793</v>
       </c>
       <c r="E3">
-        <v>-10099.214</v>
+        <v>-9869.428</v>
       </c>
       <c r="F3">
-        <v>229.786</v>
+        <v>459.572</v>
       </c>
       <c r="G3">
         <v>6462.2</v>
@@ -1539,28 +1539,28 @@
         <v>4301.8</v>
       </c>
       <c r="M3">
-        <v>11.5582358</v>
+        <v>23.1164716</v>
       </c>
       <c r="N3">
-        <v>4290.2417642</v>
+        <v>4278.6835284</v>
       </c>
       <c r="O3">
-        <v>1029.658023408</v>
+        <v>1026.884046816</v>
       </c>
       <c r="P3">
-        <v>3260.583740792</v>
+        <v>3251.799481584</v>
       </c>
       <c r="Q3">
-        <v>6150.383740792</v>
+        <v>6141.599481584</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09161961158015977</v>
+        <v>0.0919758022009243</v>
       </c>
       <c r="T3">
-        <v>0.9420994400648633</v>
+        <v>0.9494230941249063</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>372.1848277225837</v>
+        <v>186.0924138612919</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09090084615690582</v>
+        <v>0.09071599684945347</v>
       </c>
       <c r="C4">
-        <v>21728.4458109793</v>
+        <v>21521.59795035823</v>
       </c>
       <c r="D4">
-        <v>15725.8178109793</v>
+        <v>15748.75595035823</v>
       </c>
       <c r="E4">
-        <v>-9869.428</v>
+        <v>-9639.642</v>
       </c>
       <c r="F4">
-        <v>459.572</v>
+        <v>689.3579999999999</v>
       </c>
       <c r="G4">
         <v>6462.2</v>
@@ -1621,28 +1621,28 @@
         <v>4301.8</v>
       </c>
       <c r="M4">
-        <v>23.1164716</v>
+        <v>34.6747074</v>
       </c>
       <c r="N4">
-        <v>4278.6835284</v>
+        <v>4267.1252926</v>
       </c>
       <c r="O4">
-        <v>1026.884046816</v>
+        <v>1024.110070224</v>
       </c>
       <c r="P4">
-        <v>3251.799481584</v>
+        <v>3243.015222376</v>
       </c>
       <c r="Q4">
-        <v>6141.599481584</v>
+        <v>6132.815222376</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0919758022009243</v>
+        <v>0.09233933695819946</v>
       </c>
       <c r="T4">
-        <v>0.9494230941249063</v>
+        <v>0.9568977513614452</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>186.0924138612919</v>
+        <v>124.0616092408613</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09071599684945347</v>
+        <v>0.09053114754200113</v>
       </c>
       <c r="C5">
-        <v>21521.59795035823</v>
+        <v>21314.81710397265</v>
       </c>
       <c r="D5">
-        <v>15748.75595035823</v>
+        <v>15771.76110397265</v>
       </c>
       <c r="E5">
-        <v>-9639.642</v>
+        <v>-9409.856</v>
       </c>
       <c r="F5">
-        <v>689.3579999999999</v>
+        <v>919.144</v>
       </c>
       <c r="G5">
         <v>6462.2</v>
@@ -1703,28 +1703,28 @@
         <v>4301.8</v>
       </c>
       <c r="M5">
-        <v>34.6747074</v>
+        <v>46.2329432</v>
       </c>
       <c r="N5">
-        <v>4267.1252926</v>
+        <v>4255.567056800001</v>
       </c>
       <c r="O5">
-        <v>1024.110070224</v>
+        <v>1021.336093632</v>
       </c>
       <c r="P5">
-        <v>3243.015222376</v>
+        <v>3234.230963168</v>
       </c>
       <c r="Q5">
-        <v>6132.815222376</v>
+        <v>6124.030963168001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09233933695819946</v>
+        <v>0.09271044535625118</v>
       </c>
       <c r="T5">
-        <v>0.9568977513614452</v>
+        <v>0.9645281306237452</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>124.0616092408613</v>
+        <v>93.04620693064595</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09053114754200113</v>
+        <v>0.09034629823454877</v>
       </c>
       <c r="C6">
-        <v>21314.81710397265</v>
+        <v>21108.10356592734</v>
       </c>
       <c r="D6">
-        <v>15771.76110397265</v>
+        <v>15794.83356592734</v>
       </c>
       <c r="E6">
-        <v>-9409.856</v>
+        <v>-9180.07</v>
       </c>
       <c r="F6">
-        <v>919.144</v>
+        <v>1148.93</v>
       </c>
       <c r="G6">
         <v>6462.2</v>
@@ -1785,28 +1785,28 @@
         <v>4301.8</v>
       </c>
       <c r="M6">
-        <v>46.2329432</v>
+        <v>57.791179</v>
       </c>
       <c r="N6">
-        <v>4255.567056800001</v>
+        <v>4244.008821</v>
       </c>
       <c r="O6">
-        <v>1021.336093632</v>
+        <v>1018.56211704</v>
       </c>
       <c r="P6">
-        <v>3234.230963168</v>
+        <v>3225.44670396</v>
       </c>
       <c r="Q6">
-        <v>6124.030963168001</v>
+        <v>6115.246703960001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09271044535625118</v>
+        <v>0.09308936656268293</v>
       </c>
       <c r="T6">
-        <v>0.9645281306237452</v>
+        <v>0.972319149449462</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>93.04620693064595</v>
+        <v>74.43696554451675</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09034629823454877</v>
+        <v>0.09016144892709645</v>
       </c>
       <c r="C7">
-        <v>21108.10356592734</v>
+        <v>20901.45763205058</v>
       </c>
       <c r="D7">
-        <v>15794.83356592734</v>
+        <v>15817.97363205058</v>
       </c>
       <c r="E7">
-        <v>-9180.07</v>
+        <v>-8950.284</v>
       </c>
       <c r="F7">
-        <v>1148.93</v>
+        <v>1378.716</v>
       </c>
       <c r="G7">
         <v>6462.2</v>
@@ -1867,28 +1867,28 @@
         <v>4301.8</v>
       </c>
       <c r="M7">
-        <v>57.791179</v>
+        <v>69.34941480000001</v>
       </c>
       <c r="N7">
-        <v>4244.008821</v>
+        <v>4232.4505852</v>
       </c>
       <c r="O7">
-        <v>1018.56211704</v>
+        <v>1015.788140448</v>
       </c>
       <c r="P7">
-        <v>3225.44670396</v>
+        <v>3216.662444752</v>
       </c>
       <c r="Q7">
-        <v>6115.246703960001</v>
+        <v>6106.462444752</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09308936656268293</v>
+        <v>0.09347634992244302</v>
       </c>
       <c r="T7">
-        <v>0.972319149449462</v>
+        <v>0.9802759346331729</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>74.43696554451675</v>
+        <v>62.03080462043062</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09016144892709645</v>
+        <v>0.0899765996196441</v>
       </c>
       <c r="C8">
-        <v>20901.45763205058</v>
+        <v>20694.87959990678</v>
       </c>
       <c r="D8">
-        <v>15817.97363205058</v>
+        <v>15841.18159990678</v>
       </c>
       <c r="E8">
-        <v>-8950.284</v>
+        <v>-8720.498</v>
       </c>
       <c r="F8">
-        <v>1378.716</v>
+        <v>1608.502</v>
       </c>
       <c r="G8">
         <v>6462.2</v>
@@ -1949,28 +1949,28 @@
         <v>4301.8</v>
       </c>
       <c r="M8">
-        <v>69.34941479999999</v>
+        <v>80.90765059999998</v>
       </c>
       <c r="N8">
-        <v>4232.4505852</v>
+        <v>4220.8923494</v>
       </c>
       <c r="O8">
-        <v>1015.788140448</v>
+        <v>1013.014163856</v>
       </c>
       <c r="P8">
-        <v>3216.662444752</v>
+        <v>3207.878185544</v>
       </c>
       <c r="Q8">
-        <v>6106.462444752</v>
+        <v>6097.678185544</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09347634992244302</v>
+        <v>0.09387165550499366</v>
       </c>
       <c r="T8">
-        <v>0.9802759346331729</v>
+        <v>0.9884038334767483</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>62.03080462043064</v>
+        <v>53.16926110322626</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0899765996196441</v>
+        <v>0.08979175031219176</v>
       </c>
       <c r="C9">
-        <v>20694.87959990678</v>
+        <v>20488.36976880925</v>
       </c>
       <c r="D9">
-        <v>15841.18159990678</v>
+        <v>15864.45776880925</v>
       </c>
       <c r="E9">
-        <v>-8720.498</v>
+        <v>-8490.712</v>
       </c>
       <c r="F9">
-        <v>1608.502</v>
+        <v>1838.288</v>
       </c>
       <c r="G9">
         <v>6462.2</v>
@@ -2031,28 +2031,28 @@
         <v>4301.8</v>
       </c>
       <c r="M9">
-        <v>80.9076506</v>
+        <v>92.4658864</v>
       </c>
       <c r="N9">
-        <v>4220.8923494</v>
+        <v>4209.3341136</v>
       </c>
       <c r="O9">
-        <v>1013.014163856</v>
+        <v>1010.240187264</v>
       </c>
       <c r="P9">
-        <v>3207.878185544</v>
+        <v>3199.093926336</v>
       </c>
       <c r="Q9">
-        <v>6097.678185544</v>
+        <v>6088.893926336001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09387165550499366</v>
+        <v>0.09427555468716495</v>
       </c>
       <c r="T9">
-        <v>0.9884038334767483</v>
+        <v>0.996708425773445</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>53.16926110322625</v>
+        <v>46.52310346532297</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08979175031219176</v>
+        <v>0.08960690100473941</v>
       </c>
       <c r="C10">
-        <v>20488.36976880925</v>
+        <v>20281.9284398331</v>
       </c>
       <c r="D10">
-        <v>15864.45776880925</v>
+        <v>15887.8024398331</v>
       </c>
       <c r="E10">
-        <v>-8490.712</v>
+        <v>-8260.925999999999</v>
       </c>
       <c r="F10">
-        <v>1838.288</v>
+        <v>2068.074</v>
       </c>
       <c r="G10">
         <v>6462.2</v>
@@ -2113,28 +2113,28 @@
         <v>4301.8</v>
       </c>
       <c r="M10">
-        <v>92.4658864</v>
+        <v>104.0241222</v>
       </c>
       <c r="N10">
-        <v>4209.3341136</v>
+        <v>4197.7758778</v>
       </c>
       <c r="O10">
-        <v>1010.240187264</v>
+        <v>1007.466210672</v>
       </c>
       <c r="P10">
-        <v>3199.093926336</v>
+        <v>3190.309667128</v>
       </c>
       <c r="Q10">
-        <v>6088.893926336001</v>
+        <v>6080.109667128</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09427555468716495</v>
+        <v>0.0946883307744389</v>
       </c>
       <c r="T10">
-        <v>0.996708425773445</v>
+        <v>1.005195536582157</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>46.52310346532297</v>
+        <v>41.35386974695376</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08960690100473941</v>
+        <v>0.08942205169728706</v>
       </c>
       <c r="C11">
-        <v>20281.9284398331</v>
+        <v>20075.55591582814</v>
       </c>
       <c r="D11">
-        <v>15887.8024398331</v>
+        <v>15911.21591582814</v>
       </c>
       <c r="E11">
-        <v>-8260.925999999999</v>
+        <v>-8031.14</v>
       </c>
       <c r="F11">
-        <v>2068.074</v>
+        <v>2297.86</v>
       </c>
       <c r="G11">
         <v>6462.2</v>
@@ -2195,28 +2195,28 @@
         <v>4301.8</v>
       </c>
       <c r="M11">
-        <v>104.0241222</v>
+        <v>115.582358</v>
       </c>
       <c r="N11">
-        <v>4197.7758778</v>
+        <v>4186.217642000001</v>
       </c>
       <c r="O11">
-        <v>1007.466210672</v>
+        <v>1004.69223408</v>
       </c>
       <c r="P11">
-        <v>3190.309667128</v>
+        <v>3181.52540792</v>
       </c>
       <c r="Q11">
-        <v>6080.109667128</v>
+        <v>6071.325407920001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0946883307744389</v>
+        <v>0.09511027966365229</v>
       </c>
       <c r="T11">
-        <v>1.005195536582157</v>
+        <v>1.013871249853285</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>41.35386974695376</v>
+        <v>37.21848277225839</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08942205169728706</v>
+        <v>0.08923720238983471</v>
       </c>
       <c r="C12">
-        <v>20075.55591582814</v>
+        <v>19869.25250143205</v>
       </c>
       <c r="D12">
-        <v>15911.21591582814</v>
+        <v>15934.69850143205</v>
       </c>
       <c r="E12">
-        <v>-8031.139999999999</v>
+        <v>-7801.354</v>
       </c>
       <c r="F12">
-        <v>2297.86</v>
+        <v>2527.646</v>
       </c>
       <c r="G12">
         <v>6462.2</v>
@@ -2277,28 +2277,28 @@
         <v>4301.8</v>
       </c>
       <c r="M12">
-        <v>115.582358</v>
+        <v>127.1405938</v>
       </c>
       <c r="N12">
-        <v>4186.217642000001</v>
+        <v>4174.6594062</v>
       </c>
       <c r="O12">
-        <v>1004.69223408</v>
+        <v>1001.918257488</v>
       </c>
       <c r="P12">
-        <v>3181.52540792</v>
+        <v>3172.741148712</v>
       </c>
       <c r="Q12">
-        <v>6071.325407920001</v>
+        <v>6062.541148712</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09511027966365229</v>
+        <v>0.09554171055037608</v>
       </c>
       <c r="T12">
-        <v>1.013871249853285</v>
+        <v>1.022741922973202</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>37.21848277225838</v>
+        <v>33.83498433841672</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08923720238983471</v>
+        <v>0.08905235308238235</v>
       </c>
       <c r="C13">
-        <v>19869.25250143205</v>
+        <v>19663.01850308357</v>
       </c>
       <c r="D13">
-        <v>15934.69850143205</v>
+        <v>15958.25050308358</v>
       </c>
       <c r="E13">
-        <v>-7801.354</v>
+        <v>-7571.568</v>
       </c>
       <c r="F13">
-        <v>2527.646</v>
+        <v>2757.432</v>
       </c>
       <c r="G13">
         <v>6462.2</v>
@@ -2359,28 +2359,28 @@
         <v>4301.8</v>
       </c>
       <c r="M13">
-        <v>127.1405938</v>
+        <v>138.6988296</v>
       </c>
       <c r="N13">
-        <v>4174.6594062</v>
+        <v>4163.1011704</v>
       </c>
       <c r="O13">
-        <v>1001.918257488</v>
+        <v>999.1442808960001</v>
       </c>
       <c r="P13">
-        <v>3172.741148712</v>
+        <v>3163.956889504</v>
       </c>
       <c r="Q13">
-        <v>6062.541148712</v>
+        <v>6053.756889504</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09554171055037608</v>
+        <v>0.09598294668452541</v>
       </c>
       <c r="T13">
-        <v>1.022741922973202</v>
+        <v>1.03181420230039</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>33.83498433841672</v>
+        <v>31.01540231021532</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08905235308238235</v>
+        <v>0.08886750377493001</v>
       </c>
       <c r="C14">
-        <v>19663.01850308357</v>
+        <v>19456.85422903583</v>
       </c>
       <c r="D14">
-        <v>15958.25050308358</v>
+        <v>15981.87222903584</v>
       </c>
       <c r="E14">
-        <v>-7571.568</v>
+        <v>-7341.782</v>
       </c>
       <c r="F14">
-        <v>2757.432</v>
+        <v>2987.218</v>
       </c>
       <c r="G14">
         <v>6462.2</v>
@@ -2441,28 +2441,28 @@
         <v>4301.8</v>
       </c>
       <c r="M14">
-        <v>138.6988296</v>
+        <v>150.2570654</v>
       </c>
       <c r="N14">
-        <v>4163.1011704</v>
+        <v>4151.5429346</v>
       </c>
       <c r="O14">
-        <v>999.1442808960001</v>
+        <v>996.370304304</v>
       </c>
       <c r="P14">
-        <v>3163.956889504</v>
+        <v>3155.172630296</v>
       </c>
       <c r="Q14">
-        <v>6053.756889504</v>
+        <v>6044.972630296001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09598294668452541</v>
+        <v>0.09643432617808048</v>
       </c>
       <c r="T14">
-        <v>1.03181420230039</v>
+        <v>1.041095039773031</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>31.01540231021532</v>
+        <v>28.62960213250645</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08886750377493001</v>
+        <v>0.08868265446747767</v>
       </c>
       <c r="C15">
-        <v>19456.85422903583</v>
+        <v>19250.75998936979</v>
       </c>
       <c r="D15">
-        <v>15981.87222903584</v>
+        <v>16005.56398936979</v>
       </c>
       <c r="E15">
-        <v>-7341.782</v>
+        <v>-7111.996</v>
       </c>
       <c r="F15">
-        <v>2987.218</v>
+        <v>3217.004</v>
       </c>
       <c r="G15">
         <v>6462.2</v>
@@ -2523,28 +2523,28 @@
         <v>4301.8</v>
       </c>
       <c r="M15">
-        <v>150.2570654</v>
+        <v>161.8153012</v>
       </c>
       <c r="N15">
-        <v>4151.5429346</v>
+        <v>4139.9846988</v>
       </c>
       <c r="O15">
-        <v>996.370304304</v>
+        <v>993.5963277119999</v>
       </c>
       <c r="P15">
-        <v>3155.172630296</v>
+        <v>3146.388371088</v>
       </c>
       <c r="Q15">
-        <v>6044.972630296001</v>
+        <v>6036.188371088</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09643432617808048</v>
+        <v>0.09689620286916009</v>
       </c>
       <c r="T15">
-        <v>1.041095039773031</v>
+        <v>1.050591710675268</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>28.62960213250645</v>
+        <v>26.58463055161313</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08868265446747767</v>
+        <v>0.08849780516002534</v>
       </c>
       <c r="C16">
-        <v>19250.75998936979</v>
+        <v>19044.7360960078</v>
       </c>
       <c r="D16">
-        <v>16005.56398936979</v>
+        <v>16029.3260960078</v>
       </c>
       <c r="E16">
-        <v>-7111.996</v>
+        <v>-6882.209999999999</v>
       </c>
       <c r="F16">
-        <v>3217.004</v>
+        <v>3446.79</v>
       </c>
       <c r="G16">
         <v>6462.2</v>
@@ -2605,28 +2605,28 @@
         <v>4301.8</v>
       </c>
       <c r="M16">
-        <v>161.8153012</v>
+        <v>173.373537</v>
       </c>
       <c r="N16">
-        <v>4139.9846988</v>
+        <v>4128.426463</v>
       </c>
       <c r="O16">
-        <v>993.5963277119999</v>
+        <v>990.8223511199999</v>
       </c>
       <c r="P16">
-        <v>3146.388371088</v>
+        <v>3137.60411188</v>
       </c>
       <c r="Q16">
-        <v>6036.188371088</v>
+        <v>6027.40411188</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09689620286916009</v>
+        <v>0.09736894724708864</v>
       </c>
       <c r="T16">
-        <v>1.050591710675268</v>
+        <v>1.060311832657558</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>26.58463055161313</v>
+        <v>24.81232184817225</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08849780516002533</v>
+        <v>0.08831295585257298</v>
       </c>
       <c r="C17">
-        <v>19044.7360960078</v>
+        <v>18838.78286272732</v>
       </c>
       <c r="D17">
-        <v>16029.3260960078</v>
+        <v>16053.15886272732</v>
       </c>
       <c r="E17">
-        <v>-6882.210000000001</v>
+        <v>-6652.424</v>
       </c>
       <c r="F17">
-        <v>3446.79</v>
+        <v>3676.576</v>
       </c>
       <c r="G17">
         <v>6462.2</v>
@@ -2687,28 +2687,28 @@
         <v>4301.8</v>
       </c>
       <c r="M17">
-        <v>173.373537</v>
+        <v>184.9317728</v>
       </c>
       <c r="N17">
-        <v>4128.426463</v>
+        <v>4116.868227200001</v>
       </c>
       <c r="O17">
-        <v>990.8223511199999</v>
+        <v>988.0483745280001</v>
       </c>
       <c r="P17">
-        <v>3137.60411188</v>
+        <v>3128.819852672001</v>
       </c>
       <c r="Q17">
-        <v>6027.40411188</v>
+        <v>6018.619852672001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09736894724708862</v>
+        <v>0.09785294744353927</v>
       </c>
       <c r="T17">
-        <v>1.060311832657558</v>
+        <v>1.070263386115617</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>24.81232184817225</v>
+        <v>23.26155173266149</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08831295585257298</v>
+        <v>0.08812810654512064</v>
       </c>
       <c r="C18">
-        <v>18838.78286272732</v>
+        <v>18632.90060517472</v>
       </c>
       <c r="D18">
-        <v>16053.15886272732</v>
+        <v>16077.06260517472</v>
       </c>
       <c r="E18">
-        <v>-6652.424</v>
+        <v>-6422.638</v>
       </c>
       <c r="F18">
-        <v>3676.576</v>
+        <v>3906.362</v>
       </c>
       <c r="G18">
         <v>6462.2</v>
@@ -2769,28 +2769,28 @@
         <v>4301.8</v>
       </c>
       <c r="M18">
-        <v>184.9317728</v>
+        <v>196.4900086</v>
       </c>
       <c r="N18">
-        <v>4116.868227200001</v>
+        <v>4105.3099914</v>
       </c>
       <c r="O18">
-        <v>988.0483745280001</v>
+        <v>985.274397936</v>
       </c>
       <c r="P18">
-        <v>3128.819852672001</v>
+        <v>3120.035593464</v>
       </c>
       <c r="Q18">
-        <v>6018.619852672001</v>
+        <v>6009.835593464</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09785294744353927</v>
+        <v>0.09834861029532607</v>
       </c>
       <c r="T18">
-        <v>1.070263386115617</v>
+        <v>1.080454736042544</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>23.26155173266149</v>
+        <v>21.89322516015199</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08812810654512064</v>
+        <v>0.0879432572376683</v>
       </c>
       <c r="C19">
-        <v>18632.90060517472</v>
+        <v>18427.08964087919</v>
       </c>
       <c r="D19">
-        <v>16077.06260517472</v>
+        <v>16101.03764087919</v>
       </c>
       <c r="E19">
-        <v>-6422.638</v>
+        <v>-6192.852</v>
       </c>
       <c r="F19">
-        <v>3906.362</v>
+        <v>4136.148</v>
       </c>
       <c r="G19">
         <v>6462.2</v>
@@ -2851,28 +2851,28 @@
         <v>4301.8</v>
       </c>
       <c r="M19">
-        <v>196.4900086</v>
+        <v>208.0482444</v>
       </c>
       <c r="N19">
-        <v>4105.3099914</v>
+        <v>4093.7517556</v>
       </c>
       <c r="O19">
-        <v>985.274397936</v>
+        <v>982.5004213440001</v>
       </c>
       <c r="P19">
-        <v>3120.035593464</v>
+        <v>3111.251334256</v>
       </c>
       <c r="Q19">
-        <v>6009.835593464</v>
+        <v>6001.051334256001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09834861029532607</v>
+        <v>0.09885636248496134</v>
       </c>
       <c r="T19">
-        <v>1.080454736042544</v>
+        <v>1.090894655479884</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>21.89322516015199</v>
+        <v>20.67693487347688</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08794325723766831</v>
+        <v>0.08775840793021596</v>
       </c>
       <c r="C20">
-        <v>18427.08964087919</v>
+        <v>18221.35028926683</v>
       </c>
       <c r="D20">
-        <v>16101.03764087919</v>
+        <v>16125.08428926683</v>
       </c>
       <c r="E20">
-        <v>-6192.852000000001</v>
+        <v>-5963.066</v>
       </c>
       <c r="F20">
-        <v>4136.147999999999</v>
+        <v>4365.934</v>
       </c>
       <c r="G20">
         <v>6462.2</v>
@@ -2933,28 +2933,28 @@
         <v>4301.8</v>
       </c>
       <c r="M20">
-        <v>208.0482444</v>
+        <v>219.6064802</v>
       </c>
       <c r="N20">
-        <v>4093.7517556</v>
+        <v>4082.1935198</v>
       </c>
       <c r="O20">
-        <v>982.5004213440001</v>
+        <v>979.726444752</v>
       </c>
       <c r="P20">
-        <v>3111.251334256</v>
+        <v>3102.467075048</v>
       </c>
       <c r="Q20">
-        <v>6001.051334256001</v>
+        <v>5992.267075048</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09885636248496134</v>
+        <v>0.0993766517656987</v>
       </c>
       <c r="T20">
-        <v>1.090894655479884</v>
+        <v>1.101592350705801</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>20.67693487347688</v>
+        <v>19.58867514329388</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08775840793021596</v>
+        <v>0.08757355862276361</v>
       </c>
       <c r="C21">
-        <v>18221.35028926683</v>
+        <v>18015.68287167483</v>
       </c>
       <c r="D21">
-        <v>16125.08428926683</v>
+        <v>16149.20287167483</v>
       </c>
       <c r="E21">
-        <v>-5963.066</v>
+        <v>-5733.28</v>
       </c>
       <c r="F21">
-        <v>4365.934</v>
+        <v>4595.72</v>
       </c>
       <c r="G21">
         <v>6462.2</v>
@@ -3015,28 +3015,28 @@
         <v>4301.8</v>
       </c>
       <c r="M21">
-        <v>219.6064802</v>
+        <v>231.164716</v>
       </c>
       <c r="N21">
-        <v>4082.1935198</v>
+        <v>4070.635284</v>
       </c>
       <c r="O21">
-        <v>979.726444752</v>
+        <v>976.95246816</v>
       </c>
       <c r="P21">
-        <v>3102.467075048</v>
+        <v>3093.68281584</v>
       </c>
       <c r="Q21">
-        <v>5992.267075048</v>
+        <v>5983.48281584</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0993766517656987</v>
+        <v>0.09990994827845451</v>
       </c>
       <c r="T21">
-        <v>1.101592350705801</v>
+        <v>1.112557488312365</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>19.58867514329388</v>
+        <v>18.60924138612919</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08757355862276361</v>
+        <v>0.08738870931531126</v>
       </c>
       <c r="C22">
-        <v>18015.68287167483</v>
+        <v>17810.08771136578</v>
       </c>
       <c r="D22">
-        <v>16149.20287167483</v>
+        <v>16173.39371136578</v>
       </c>
       <c r="E22">
-        <v>-5733.28</v>
+        <v>-5503.494</v>
       </c>
       <c r="F22">
-        <v>4595.72</v>
+        <v>4825.506</v>
       </c>
       <c r="G22">
         <v>6462.2</v>
@@ -3097,28 +3097,28 @@
         <v>4301.8</v>
       </c>
       <c r="M22">
-        <v>231.164716</v>
+        <v>242.7229518</v>
       </c>
       <c r="N22">
-        <v>4070.635284</v>
+        <v>4059.0770482</v>
       </c>
       <c r="O22">
-        <v>976.95246816</v>
+        <v>974.178491568</v>
       </c>
       <c r="P22">
-        <v>3093.68281584</v>
+        <v>3084.898556632</v>
       </c>
       <c r="Q22">
-        <v>5983.48281584</v>
+        <v>5974.698556632</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09990994827845451</v>
+        <v>0.1004567459687484</v>
       </c>
       <c r="T22">
-        <v>1.112557488312365</v>
+        <v>1.123800224339349</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>18.60924138612919</v>
+        <v>17.72308703440875</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08738870931531126</v>
+        <v>0.08720386000785892</v>
       </c>
       <c r="C23">
-        <v>17810.08771136578</v>
+        <v>17604.5651335421</v>
       </c>
       <c r="D23">
-        <v>16173.39371136578</v>
+        <v>16197.6571335421</v>
       </c>
       <c r="E23">
-        <v>-5503.494000000001</v>
+        <v>-5273.708000000001</v>
       </c>
       <c r="F23">
-        <v>4825.505999999999</v>
+        <v>5055.291999999999</v>
       </c>
       <c r="G23">
         <v>6462.2</v>
@@ -3179,28 +3179,28 @@
         <v>4301.8</v>
       </c>
       <c r="M23">
-        <v>242.7229517999999</v>
+        <v>254.2811876</v>
       </c>
       <c r="N23">
-        <v>4059.0770482</v>
+        <v>4047.5188124</v>
       </c>
       <c r="O23">
-        <v>974.178491568</v>
+        <v>971.404514976</v>
       </c>
       <c r="P23">
-        <v>3084.898556632</v>
+        <v>3076.114297424</v>
       </c>
       <c r="Q23">
-        <v>5974.698556632</v>
+        <v>5965.914297424</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1004567459687484</v>
+        <v>0.1010175641126396</v>
       </c>
       <c r="T23">
-        <v>1.123800224339349</v>
+        <v>1.135331235649076</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>17.72308703440876</v>
+        <v>16.91749216920836</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08720386000785892</v>
+        <v>0.08701901070040657</v>
       </c>
       <c r="C24">
-        <v>17604.5651335421</v>
+        <v>17399.11546536062</v>
       </c>
       <c r="D24">
-        <v>16197.6571335421</v>
+        <v>16221.99346536062</v>
       </c>
       <c r="E24">
-        <v>-5273.708000000001</v>
+        <v>-5043.922</v>
       </c>
       <c r="F24">
-        <v>5055.291999999999</v>
+        <v>5285.078</v>
       </c>
       <c r="G24">
         <v>6462.2</v>
@@ -3261,28 +3261,28 @@
         <v>4301.8</v>
       </c>
       <c r="M24">
-        <v>254.2811876</v>
+        <v>265.8394234</v>
       </c>
       <c r="N24">
-        <v>4047.5188124</v>
+        <v>4035.9605766</v>
       </c>
       <c r="O24">
-        <v>971.404514976</v>
+        <v>968.630538384</v>
       </c>
       <c r="P24">
-        <v>3076.114297424</v>
+        <v>3067.330038216001</v>
       </c>
       <c r="Q24">
-        <v>5965.914297424</v>
+        <v>5957.130038216001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1010175641126396</v>
+        <v>0.101592948961567</v>
       </c>
       <c r="T24">
-        <v>1.135331235649076</v>
+        <v>1.147161753746069</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>16.91749216920836</v>
+        <v>16.18194903141669</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08701901070040657</v>
+        <v>0.08683416139295423</v>
       </c>
       <c r="C25">
-        <v>17399.11546536062</v>
+        <v>17193.73903594732</v>
       </c>
       <c r="D25">
-        <v>16221.99346536062</v>
+        <v>16246.40303594732</v>
       </c>
       <c r="E25">
-        <v>-5043.922</v>
+        <v>-4814.136</v>
       </c>
       <c r="F25">
-        <v>5285.078</v>
+        <v>5514.864</v>
       </c>
       <c r="G25">
         <v>6462.2</v>
@@ -3343,28 +3343,28 @@
         <v>4301.8</v>
       </c>
       <c r="M25">
-        <v>265.8394234</v>
+        <v>277.3976592</v>
       </c>
       <c r="N25">
-        <v>4035.9605766</v>
+        <v>4024.4023408</v>
       </c>
       <c r="O25">
-        <v>968.630538384</v>
+        <v>965.856561792</v>
       </c>
       <c r="P25">
-        <v>3067.330038216001</v>
+        <v>3058.545779008</v>
       </c>
       <c r="Q25">
-        <v>5957.130038216001</v>
+        <v>5948.345779008001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.101592948961567</v>
+        <v>0.102183475517045</v>
       </c>
       <c r="T25">
-        <v>1.147161753746069</v>
+        <v>1.159303601266666</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>16.18194903141669</v>
+        <v>15.50770115510766</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08683416139295423</v>
+        <v>0.08664931208550188</v>
       </c>
       <c r="C26">
-        <v>17193.73903594732</v>
+        <v>16988.43617641211</v>
       </c>
       <c r="D26">
-        <v>16246.40303594732</v>
+        <v>16270.88617641211</v>
       </c>
       <c r="E26">
-        <v>-4814.136</v>
+        <v>-4584.35</v>
       </c>
       <c r="F26">
-        <v>5514.864</v>
+        <v>5744.65</v>
       </c>
       <c r="G26">
         <v>6462.2</v>
@@ -3425,28 +3425,28 @@
         <v>4301.8</v>
       </c>
       <c r="M26">
-        <v>277.3976592</v>
+        <v>288.9558949999999</v>
       </c>
       <c r="N26">
-        <v>4024.4023408</v>
+        <v>4012.844105</v>
       </c>
       <c r="O26">
-        <v>965.856561792</v>
+        <v>963.0825852</v>
       </c>
       <c r="P26">
-        <v>3058.545779008</v>
+        <v>3049.7615198</v>
       </c>
       <c r="Q26">
-        <v>5948.345779008001</v>
+        <v>5939.5615198</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.102183475517045</v>
+        <v>0.1027897494473358</v>
       </c>
       <c r="T26">
-        <v>1.159303601266666</v>
+        <v>1.171769231387813</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>15.50770115510766</v>
+        <v>14.88739310890335</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08664931208550188</v>
+        <v>0.08646446277804953</v>
       </c>
       <c r="C27">
-        <v>16988.43617641211</v>
+        <v>16783.20721986383</v>
       </c>
       <c r="D27">
-        <v>16270.88617641211</v>
+        <v>16295.44321986382</v>
       </c>
       <c r="E27">
-        <v>-4584.35</v>
+        <v>-4354.564</v>
       </c>
       <c r="F27">
-        <v>5744.65</v>
+        <v>5974.436</v>
       </c>
       <c r="G27">
         <v>6462.2</v>
@@ -3507,28 +3507,28 @@
         <v>4301.8</v>
       </c>
       <c r="M27">
-        <v>288.9558949999999</v>
+        <v>300.5141308</v>
       </c>
       <c r="N27">
-        <v>4012.844105</v>
+        <v>4001.2858692</v>
       </c>
       <c r="O27">
-        <v>963.0825852</v>
+        <v>960.308608608</v>
       </c>
       <c r="P27">
-        <v>3049.7615198</v>
+        <v>3040.977260592</v>
       </c>
       <c r="Q27">
-        <v>5939.5615198</v>
+        <v>5930.777260592</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1027897494473358</v>
+        <v>0.1034124091595264</v>
       </c>
       <c r="T27">
-        <v>1.171769231387813</v>
+        <v>1.184571770431153</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>14.88739310890335</v>
+        <v>14.31480106625322</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08646446277804953</v>
+        <v>0.08627961347059718</v>
       </c>
       <c r="C28">
-        <v>16783.20721986383</v>
+        <v>16578.05250142535</v>
       </c>
       <c r="D28">
-        <v>16295.44321986382</v>
+        <v>16320.07450142535</v>
       </c>
       <c r="E28">
-        <v>-4354.564</v>
+        <v>-4124.778</v>
       </c>
       <c r="F28">
-        <v>5974.436</v>
+        <v>6204.222</v>
       </c>
       <c r="G28">
         <v>6462.2</v>
@@ -3589,28 +3589,28 @@
         <v>4301.8</v>
       </c>
       <c r="M28">
-        <v>300.5141308</v>
+        <v>312.0723666</v>
       </c>
       <c r="N28">
-        <v>4001.2858692</v>
+        <v>3989.7276334</v>
       </c>
       <c r="O28">
-        <v>960.308608608</v>
+        <v>957.534632016</v>
       </c>
       <c r="P28">
-        <v>3040.977260592</v>
+        <v>3032.193001384</v>
       </c>
       <c r="Q28">
-        <v>5930.777260592</v>
+        <v>5921.993001384</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1034124091595264</v>
+        <v>0.104052128041914</v>
       </c>
       <c r="T28">
-        <v>1.184571770431153</v>
+        <v>1.197725063968831</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>14.31480106625322</v>
+        <v>13.78462324898459</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08627961347059718</v>
+        <v>0.08609476416314485</v>
       </c>
       <c r="C29">
-        <v>16578.05250142535</v>
+        <v>16372.97235824885</v>
       </c>
       <c r="D29">
-        <v>16320.07450142535</v>
+        <v>16344.78035824885</v>
       </c>
       <c r="E29">
-        <v>-4124.778</v>
+        <v>-3894.992</v>
       </c>
       <c r="F29">
-        <v>6204.222</v>
+        <v>6434.008</v>
       </c>
       <c r="G29">
         <v>6462.2</v>
@@ -3671,28 +3671,28 @@
         <v>4301.8</v>
       </c>
       <c r="M29">
-        <v>312.0723666</v>
+        <v>323.6306024</v>
       </c>
       <c r="N29">
-        <v>3989.7276334</v>
+        <v>3978.1693976</v>
       </c>
       <c r="O29">
-        <v>957.534632016</v>
+        <v>954.760655424</v>
       </c>
       <c r="P29">
-        <v>3032.193001384</v>
+        <v>3023.408742176</v>
       </c>
       <c r="Q29">
-        <v>5921.993001384</v>
+        <v>5913.208742176001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.104052128041914</v>
+        <v>0.1047096168932567</v>
       </c>
       <c r="T29">
-        <v>1.197725063968831</v>
+        <v>1.211243726771445</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>13.78462324898459</v>
+        <v>13.29231527580656</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08609476416314485</v>
+        <v>0.08590991485569251</v>
       </c>
       <c r="C30">
-        <v>16372.97235824885</v>
+        <v>16167.96712953113</v>
       </c>
       <c r="D30">
-        <v>16344.78035824885</v>
+        <v>16369.56112953113</v>
       </c>
       <c r="E30">
-        <v>-3894.992</v>
+        <v>-3665.205999999999</v>
       </c>
       <c r="F30">
-        <v>6434.008</v>
+        <v>6663.794000000001</v>
       </c>
       <c r="G30">
         <v>6462.2</v>
@@ -3753,28 +3753,28 @@
         <v>4301.8</v>
       </c>
       <c r="M30">
-        <v>323.6306024</v>
+        <v>335.1888382</v>
       </c>
       <c r="N30">
-        <v>3978.1693976</v>
+        <v>3966.6111618</v>
       </c>
       <c r="O30">
-        <v>954.760655424</v>
+        <v>951.9866788319999</v>
       </c>
       <c r="P30">
-        <v>3023.408742176</v>
+        <v>3014.624482968</v>
       </c>
       <c r="Q30">
-        <v>5913.208742176001</v>
+        <v>5904.424482968</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1047096168932567</v>
+        <v>0.1053856265573134</v>
       </c>
       <c r="T30">
-        <v>1.211243726771445</v>
+        <v>1.22514319697695</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>13.29231527580656</v>
+        <v>12.83395957664082</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08590991485569249</v>
+        <v>0.08572506554824015</v>
       </c>
       <c r="C31">
-        <v>16167.96712953113</v>
+        <v>15963.03715652921</v>
       </c>
       <c r="D31">
-        <v>16369.56112953113</v>
+        <v>16394.41715652921</v>
       </c>
       <c r="E31">
-        <v>-3665.206000000001</v>
+        <v>-3435.420000000001</v>
       </c>
       <c r="F31">
-        <v>6663.793999999999</v>
+        <v>6893.579999999999</v>
       </c>
       <c r="G31">
         <v>6462.2</v>
@@ -3835,28 +3835,28 @@
         <v>4301.8</v>
       </c>
       <c r="M31">
-        <v>335.1888381999999</v>
+        <v>346.7470739999999</v>
       </c>
       <c r="N31">
-        <v>3966.6111618</v>
+        <v>3955.052926</v>
       </c>
       <c r="O31">
-        <v>951.9866788320001</v>
+        <v>949.21270224</v>
       </c>
       <c r="P31">
-        <v>3014.624482968</v>
+        <v>3005.84022376</v>
       </c>
       <c r="Q31">
-        <v>5904.424482968001</v>
+        <v>5895.64022376</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1053856265573134</v>
+        <v>0.1060809507832002</v>
       </c>
       <c r="T31">
-        <v>1.22514319697695</v>
+        <v>1.239439794902611</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>12.83395957664082</v>
+        <v>12.40616092408613</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08572506554824015</v>
+        <v>0.08554021624078781</v>
       </c>
       <c r="C32">
-        <v>15963.03715652921</v>
+        <v>15758.18278257594</v>
       </c>
       <c r="D32">
-        <v>16394.41715652921</v>
+        <v>16419.34878257594</v>
       </c>
       <c r="E32">
-        <v>-3435.420000000001</v>
+        <v>-3205.634000000001</v>
       </c>
       <c r="F32">
-        <v>6893.579999999999</v>
+        <v>7123.365999999999</v>
       </c>
       <c r="G32">
         <v>6462.2</v>
@@ -3917,28 +3917,28 @@
         <v>4301.8</v>
       </c>
       <c r="M32">
-        <v>346.7470739999999</v>
+        <v>358.3053097999999</v>
       </c>
       <c r="N32">
-        <v>3955.052926</v>
+        <v>3943.4946902</v>
       </c>
       <c r="O32">
-        <v>949.21270224</v>
+        <v>946.4387256479999</v>
       </c>
       <c r="P32">
-        <v>3005.84022376</v>
+        <v>2997.055964552</v>
       </c>
       <c r="Q32">
-        <v>5895.64022376</v>
+        <v>5886.855964552</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1060809507832002</v>
+        <v>0.1067964293344751</v>
       </c>
       <c r="T32">
-        <v>1.239439794902611</v>
+        <v>1.254150786971045</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>12.40616092408613</v>
+        <v>12.00596218459948</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08554021624078781</v>
+        <v>0.08535536693333547</v>
       </c>
       <c r="C33">
-        <v>15758.18278257594</v>
+        <v>15553.40435309584</v>
       </c>
       <c r="D33">
-        <v>16419.34878257594</v>
+        <v>16444.35635309584</v>
       </c>
       <c r="E33">
-        <v>-3205.634000000001</v>
+        <v>-2975.848</v>
       </c>
       <c r="F33">
-        <v>7123.365999999999</v>
+        <v>7353.152</v>
       </c>
       <c r="G33">
         <v>6462.2</v>
@@ -3999,28 +3999,28 @@
         <v>4301.8</v>
       </c>
       <c r="M33">
-        <v>358.3053097999999</v>
+        <v>369.8635456</v>
       </c>
       <c r="N33">
-        <v>3943.4946902</v>
+        <v>3931.9364544</v>
       </c>
       <c r="O33">
-        <v>946.4387256479999</v>
+        <v>943.664749056</v>
       </c>
       <c r="P33">
-        <v>2997.055964552</v>
+        <v>2988.271705344</v>
       </c>
       <c r="Q33">
-        <v>5886.855964552</v>
+        <v>5878.071705344</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1067964293344751</v>
+        <v>0.1075329513725522</v>
       </c>
       <c r="T33">
-        <v>1.254150786971045</v>
+        <v>1.269294455276786</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>12.00596218459948</v>
+        <v>11.63077586633074</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08535536693333547</v>
+        <v>0.0851705176258831</v>
       </c>
       <c r="C34">
-        <v>15553.40435309584</v>
+        <v>15348.70221562104</v>
       </c>
       <c r="D34">
-        <v>16444.35635309584</v>
+        <v>16469.44021562104</v>
       </c>
       <c r="E34">
-        <v>-2975.848</v>
+        <v>-2746.062</v>
       </c>
       <c r="F34">
-        <v>7353.152</v>
+        <v>7582.938</v>
       </c>
       <c r="G34">
         <v>6462.2</v>
@@ -4081,28 +4081,28 @@
         <v>4301.8</v>
       </c>
       <c r="M34">
-        <v>369.8635456</v>
+        <v>381.4217814</v>
       </c>
       <c r="N34">
-        <v>3931.9364544</v>
+        <v>3920.3782186</v>
       </c>
       <c r="O34">
-        <v>943.664749056</v>
+        <v>940.8907724640001</v>
       </c>
       <c r="P34">
-        <v>2988.271705344</v>
+        <v>2979.487446136</v>
       </c>
       <c r="Q34">
-        <v>5878.071705344</v>
+        <v>5869.287446136001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1075329513725522</v>
+        <v>0.1082914591431091</v>
       </c>
       <c r="T34">
-        <v>1.269294455276786</v>
+        <v>1.284890173382699</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>11.63077586633074</v>
+        <v>11.27832811280557</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0851705176258831</v>
+        <v>0.08498566831843075</v>
       </c>
       <c r="C35">
-        <v>15348.70221562104</v>
+        <v>15144.07671980738</v>
       </c>
       <c r="D35">
-        <v>16469.44021562104</v>
+        <v>16494.60071980738</v>
       </c>
       <c r="E35">
-        <v>-2746.062</v>
+        <v>-2516.276</v>
       </c>
       <c r="F35">
-        <v>7582.938</v>
+        <v>7812.724</v>
       </c>
       <c r="G35">
         <v>6462.2</v>
@@ -4163,28 +4163,28 @@
         <v>4301.8</v>
       </c>
       <c r="M35">
-        <v>381.4217814</v>
+        <v>392.9800172</v>
       </c>
       <c r="N35">
-        <v>3920.3782186</v>
+        <v>3908.8199828</v>
       </c>
       <c r="O35">
-        <v>940.8907724640001</v>
+        <v>938.116795872</v>
       </c>
       <c r="P35">
-        <v>2979.487446136</v>
+        <v>2970.703186928</v>
       </c>
       <c r="Q35">
-        <v>5869.287446136001</v>
+        <v>5860.503186928</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1082914591431091</v>
+        <v>0.1090729519976224</v>
       </c>
       <c r="T35">
-        <v>1.284890173382699</v>
+        <v>1.300958489006973</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.27832811280557</v>
+        <v>10.94661258007599</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08498566831843075</v>
+        <v>0.08480081901097841</v>
       </c>
       <c r="C36">
-        <v>15144.07671980738</v>
+        <v>14939.52821745065</v>
       </c>
       <c r="D36">
-        <v>16494.60071980738</v>
+        <v>16519.83821745065</v>
       </c>
       <c r="E36">
-        <v>-2516.276</v>
+        <v>-2286.49</v>
       </c>
       <c r="F36">
-        <v>7812.724</v>
+        <v>8042.51</v>
       </c>
       <c r="G36">
         <v>6462.2</v>
@@ -4245,28 +4245,28 @@
         <v>4301.8</v>
       </c>
       <c r="M36">
-        <v>392.9800172</v>
+        <v>404.538253</v>
       </c>
       <c r="N36">
-        <v>3908.8199828</v>
+        <v>3897.261747</v>
       </c>
       <c r="O36">
-        <v>938.116795872</v>
+        <v>935.34281928</v>
       </c>
       <c r="P36">
-        <v>2970.703186928</v>
+        <v>2961.91892772</v>
       </c>
       <c r="Q36">
-        <v>5860.503186928</v>
+        <v>5851.71892772</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1090729519976224</v>
+        <v>0.1098784907861207</v>
       </c>
       <c r="T36">
-        <v>1.300958489006973</v>
+        <v>1.317521214342762</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.94661258007599</v>
+        <v>10.63385222064525</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08480081901097841</v>
+        <v>0.08461596970352607</v>
       </c>
       <c r="C37">
-        <v>14939.52821745065</v>
+        <v>14735.05706250301</v>
       </c>
       <c r="D37">
-        <v>16519.83821745065</v>
+        <v>16545.15306250301</v>
       </c>
       <c r="E37">
-        <v>-2286.49</v>
+        <v>-2056.704</v>
       </c>
       <c r="F37">
-        <v>8042.51</v>
+        <v>8272.296</v>
       </c>
       <c r="G37">
         <v>6462.2</v>
@@ -4327,28 +4327,28 @@
         <v>4301.8</v>
       </c>
       <c r="M37">
-        <v>404.538253</v>
+        <v>416.0964888</v>
       </c>
       <c r="N37">
-        <v>3897.261747</v>
+        <v>3885.7035112</v>
       </c>
       <c r="O37">
-        <v>935.34281928</v>
+        <v>932.568842688</v>
       </c>
       <c r="P37">
-        <v>2961.91892772</v>
+        <v>2953.134668512</v>
       </c>
       <c r="Q37">
-        <v>5851.71892772</v>
+        <v>5842.934668512</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1098784907861207</v>
+        <v>0.1107092026617595</v>
       </c>
       <c r="T37">
-        <v>1.317521214342762</v>
+        <v>1.334601524845295</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>10.63385222064525</v>
+        <v>10.33846743673844</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08461596970352608</v>
+        <v>0.08443112039607374</v>
       </c>
       <c r="C38">
-        <v>14735.05706250302</v>
+        <v>14530.66361108952</v>
       </c>
       <c r="D38">
-        <v>16545.15306250301</v>
+        <v>16570.54561108952</v>
       </c>
       <c r="E38">
-        <v>-2056.704000000002</v>
+        <v>-1826.918000000001</v>
       </c>
       <c r="F38">
-        <v>8272.295999999998</v>
+        <v>8502.081999999999</v>
       </c>
       <c r="G38">
         <v>6462.2</v>
@@ -4409,28 +4409,28 @@
         <v>4301.8</v>
       </c>
       <c r="M38">
-        <v>416.0964887999999</v>
+        <v>427.6547245999999</v>
       </c>
       <c r="N38">
-        <v>3885.7035112</v>
+        <v>3874.1452754</v>
       </c>
       <c r="O38">
-        <v>932.568842688</v>
+        <v>929.794866096</v>
       </c>
       <c r="P38">
-        <v>2953.134668512</v>
+        <v>2944.350409304</v>
       </c>
       <c r="Q38">
-        <v>5842.934668512</v>
+        <v>5834.150409304</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1107092026617595</v>
+        <v>0.1115662863429742</v>
       </c>
       <c r="T38">
-        <v>1.334601524845295</v>
+        <v>1.352224067427274</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.33846743673844</v>
+        <v>10.05904939790767</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08443112039607374</v>
+        <v>0.08424627108862139</v>
       </c>
       <c r="C39">
-        <v>14530.66361108952</v>
+        <v>14326.34822152483</v>
       </c>
       <c r="D39">
-        <v>16570.54561108952</v>
+        <v>16596.01622152483</v>
       </c>
       <c r="E39">
-        <v>-1826.918000000001</v>
+        <v>-1597.132</v>
       </c>
       <c r="F39">
-        <v>8502.081999999999</v>
+        <v>8731.868</v>
       </c>
       <c r="G39">
         <v>6462.2</v>
@@ -4491,28 +4491,28 @@
         <v>4301.8</v>
       </c>
       <c r="M39">
-        <v>427.6547245999999</v>
+        <v>439.2129604</v>
       </c>
       <c r="N39">
-        <v>3874.1452754</v>
+        <v>3862.5870396</v>
       </c>
       <c r="O39">
-        <v>929.794866096</v>
+        <v>927.020889504</v>
       </c>
       <c r="P39">
-        <v>2944.350409304</v>
+        <v>2935.566150096</v>
       </c>
       <c r="Q39">
-        <v>5834.150409304</v>
+        <v>5825.366150096001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1115662863429742</v>
+        <v>0.1124510178848732</v>
       </c>
       <c r="T39">
-        <v>1.352224067427274</v>
+        <v>1.3704150791248</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.05904939790767</v>
+        <v>9.794337571646942</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08424627108862139</v>
+        <v>0.08406142178116904</v>
       </c>
       <c r="C40">
-        <v>14326.34822152483</v>
+        <v>14122.11125433005</v>
       </c>
       <c r="D40">
-        <v>16596.01622152483</v>
+        <v>16621.56525433005</v>
       </c>
       <c r="E40">
-        <v>-1597.132</v>
+        <v>-1367.346</v>
       </c>
       <c r="F40">
-        <v>8731.868</v>
+        <v>8961.654</v>
       </c>
       <c r="G40">
         <v>6462.2</v>
@@ -4573,28 +4573,28 @@
         <v>4301.8</v>
       </c>
       <c r="M40">
-        <v>439.2129604</v>
+        <v>450.7711962</v>
       </c>
       <c r="N40">
-        <v>3862.5870396</v>
+        <v>3851.0288038</v>
       </c>
       <c r="O40">
-        <v>927.020889504</v>
+        <v>924.2469129120001</v>
       </c>
       <c r="P40">
-        <v>2935.566150096</v>
+        <v>2926.781890888</v>
       </c>
       <c r="Q40">
-        <v>5825.366150096001</v>
+        <v>5816.581890888001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1124510178848732</v>
+        <v>0.1133647570183099</v>
       </c>
       <c r="T40">
-        <v>1.3704150791248</v>
+        <v>1.38920251743536</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>9.794337571646942</v>
+        <v>9.543200710835482</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08406142178116904</v>
+        <v>0.08387657247371672</v>
       </c>
       <c r="C41">
-        <v>14122.11125433005</v>
+        <v>13917.95307224975</v>
       </c>
       <c r="D41">
-        <v>16621.56525433005</v>
+        <v>16647.19307224975</v>
       </c>
       <c r="E41">
-        <v>-1367.346</v>
+        <v>-1137.559999999999</v>
       </c>
       <c r="F41">
-        <v>8961.654</v>
+        <v>9191.440000000001</v>
       </c>
       <c r="G41">
         <v>6462.2</v>
@@ -4655,28 +4655,28 @@
         <v>4301.8</v>
       </c>
       <c r="M41">
-        <v>450.7711962</v>
+        <v>462.329432</v>
       </c>
       <c r="N41">
-        <v>3851.0288038</v>
+        <v>3839.470568</v>
       </c>
       <c r="O41">
-        <v>924.2469129120001</v>
+        <v>921.47293632</v>
       </c>
       <c r="P41">
-        <v>2926.781890888</v>
+        <v>2917.99763168</v>
       </c>
       <c r="Q41">
-        <v>5816.581890888001</v>
+        <v>5807.79763168</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1133647570183099</v>
+        <v>0.1143089541228612</v>
       </c>
       <c r="T41">
-        <v>1.38920251743536</v>
+        <v>1.408616203689605</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>9.543200710835482</v>
+        <v>9.304620693064594</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08387657247371672</v>
+        <v>0.08369172316626436</v>
       </c>
       <c r="C42">
-        <v>13917.95307224975</v>
+        <v>13713.87404026915</v>
       </c>
       <c r="D42">
-        <v>16647.19307224975</v>
+        <v>16672.90004026915</v>
       </c>
       <c r="E42">
-        <v>-1137.559999999999</v>
+        <v>-907.7739999999994</v>
       </c>
       <c r="F42">
-        <v>9191.440000000001</v>
+        <v>9421.226000000001</v>
       </c>
       <c r="G42">
         <v>6462.2</v>
@@ -4737,28 +4737,28 @@
         <v>4301.8</v>
       </c>
       <c r="M42">
-        <v>462.329432</v>
+        <v>473.8876678</v>
       </c>
       <c r="N42">
-        <v>3839.470568</v>
+        <v>3827.9123322</v>
       </c>
       <c r="O42">
-        <v>921.47293632</v>
+        <v>918.698959728</v>
       </c>
       <c r="P42">
-        <v>2917.99763168</v>
+        <v>2909.213372472</v>
       </c>
       <c r="Q42">
-        <v>5807.79763168</v>
+        <v>5799.013372472</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1143089541228612</v>
+        <v>0.1152851579089226</v>
       </c>
       <c r="T42">
-        <v>1.408616203689605</v>
+        <v>1.428687981003316</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>9.304620693064594</v>
+        <v>9.077678724941066</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08369172316626436</v>
+        <v>0.083506873858812</v>
       </c>
       <c r="C43">
-        <v>13713.87404026915</v>
+        <v>13509.87452563142</v>
       </c>
       <c r="D43">
-        <v>16672.90004026915</v>
+        <v>16698.68652563142</v>
       </c>
       <c r="E43">
-        <v>-907.7739999999994</v>
+        <v>-677.9879999999994</v>
       </c>
       <c r="F43">
-        <v>9421.226000000001</v>
+        <v>9651.012000000001</v>
       </c>
       <c r="G43">
         <v>6462.2</v>
@@ -4819,28 +4819,28 @@
         <v>4301.8</v>
       </c>
       <c r="M43">
-        <v>473.8876678</v>
+        <v>485.4459036</v>
       </c>
       <c r="N43">
-        <v>3827.9123322</v>
+        <v>3816.3540964</v>
       </c>
       <c r="O43">
-        <v>918.698959728</v>
+        <v>915.924983136</v>
       </c>
       <c r="P43">
-        <v>2909.213372472</v>
+        <v>2900.429113264</v>
       </c>
       <c r="Q43">
-        <v>5799.013372472</v>
+        <v>5790.229113264</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1152851579089226</v>
+        <v>0.1162950238945035</v>
       </c>
       <c r="T43">
-        <v>1.428687981003316</v>
+        <v>1.449451888569225</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>9.077678724941066</v>
+        <v>8.861543517204375</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08350687385881202</v>
+        <v>0.08381222455135966</v>
       </c>
       <c r="C44">
-        <v>13509.87452563142</v>
+        <v>13237.53492962819</v>
       </c>
       <c r="D44">
-        <v>16698.68652563142</v>
+        <v>16656.13292962819</v>
       </c>
       <c r="E44">
-        <v>-677.9880000000012</v>
+        <v>-448.2020000000011</v>
       </c>
       <c r="F44">
-        <v>9651.011999999999</v>
+        <v>9880.797999999999</v>
       </c>
       <c r="G44">
         <v>6462.2</v>
@@ -4901,45 +4901,45 @@
         <v>4301.8</v>
       </c>
       <c r="M44">
-        <v>485.4459035999999</v>
+        <v>511.8253363999999</v>
       </c>
       <c r="N44">
-        <v>3816.3540964</v>
+        <v>3789.9746636</v>
       </c>
       <c r="O44">
-        <v>915.924983136</v>
+        <v>909.5939192640001</v>
       </c>
       <c r="P44">
-        <v>2900.429113264</v>
+        <v>2880.380744336</v>
       </c>
       <c r="Q44">
-        <v>5790.229113264</v>
+        <v>5770.180744336</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1162950238945035</v>
+        <v>0.1173403237743152</v>
       </c>
       <c r="T44">
-        <v>1.449451888569224</v>
+        <v>1.47094435429534</v>
       </c>
       <c r="U44">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V44">
         <v>0.24</v>
       </c>
       <c r="W44">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y44">
-        <v>8.861543517204378</v>
+        <v>8.404820344098935</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08381222455135966</v>
+        <v>0.08363877524390732</v>
       </c>
       <c r="C45">
-        <v>13237.53492962819</v>
+        <v>13031.8941349541</v>
       </c>
       <c r="D45">
-        <v>16656.13292962819</v>
+        <v>16680.2781349541</v>
       </c>
       <c r="E45">
-        <v>-448.2020000000011</v>
+        <v>-218.4160000000011</v>
       </c>
       <c r="F45">
-        <v>9880.797999999999</v>
+        <v>10110.584</v>
       </c>
       <c r="G45">
         <v>6462.2</v>
@@ -4983,28 +4983,28 @@
         <v>4301.8</v>
       </c>
       <c r="M45">
-        <v>511.8253363999999</v>
+        <v>523.7282511999999</v>
       </c>
       <c r="N45">
-        <v>3789.9746636</v>
+        <v>3778.0717488</v>
       </c>
       <c r="O45">
-        <v>909.5939192640001</v>
+        <v>906.737219712</v>
       </c>
       <c r="P45">
-        <v>2880.380744336</v>
+        <v>2871.334529088</v>
       </c>
       <c r="Q45">
-        <v>5770.180744336</v>
+        <v>5761.134529088</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1173403237743152</v>
+        <v>0.1184229557926916</v>
       </c>
       <c r="T45">
-        <v>1.47094435429534</v>
+        <v>1.493204408083102</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.404820344098935</v>
+        <v>8.213801699914868</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08363877524390732</v>
+        <v>0.08346532593645496</v>
       </c>
       <c r="C46">
-        <v>13031.8941349541</v>
+        <v>12826.32344506242</v>
       </c>
       <c r="D46">
-        <v>16680.2781349541</v>
+        <v>16704.49344506242</v>
       </c>
       <c r="E46">
-        <v>-218.4160000000011</v>
+        <v>11.36999999999898</v>
       </c>
       <c r="F46">
-        <v>10110.584</v>
+        <v>10340.37</v>
       </c>
       <c r="G46">
         <v>6462.2</v>
@@ -5065,28 +5065,28 @@
         <v>4301.8</v>
       </c>
       <c r="M46">
-        <v>523.7282511999999</v>
+        <v>535.6311659999999</v>
       </c>
       <c r="N46">
-        <v>3778.0717488</v>
+        <v>3766.168834</v>
       </c>
       <c r="O46">
-        <v>906.737219712</v>
+        <v>903.8805201599999</v>
       </c>
       <c r="P46">
-        <v>2871.334529088</v>
+        <v>2862.28831384</v>
       </c>
       <c r="Q46">
-        <v>5761.134529088</v>
+        <v>5752.08831384</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1184229557926916</v>
+        <v>0.1195449562480999</v>
       </c>
       <c r="T46">
-        <v>1.493204408083102</v>
+        <v>1.516273918372238</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.213801699914868</v>
+        <v>8.031272773250093</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08346532593645496</v>
+        <v>0.08329187662900264</v>
       </c>
       <c r="C47">
-        <v>12826.32344506242</v>
+        <v>12620.82316571731</v>
       </c>
       <c r="D47">
-        <v>16704.49344506242</v>
+        <v>16728.77916571731</v>
       </c>
       <c r="E47">
-        <v>11.36999999999898</v>
+        <v>241.155999999999</v>
       </c>
       <c r="F47">
-        <v>10340.37</v>
+        <v>10570.156</v>
       </c>
       <c r="G47">
         <v>6462.2</v>
@@ -5147,28 +5147,28 @@
         <v>4301.8</v>
       </c>
       <c r="M47">
-        <v>535.6311659999999</v>
+        <v>547.5340808</v>
       </c>
       <c r="N47">
-        <v>3766.168834</v>
+        <v>3754.2659192</v>
       </c>
       <c r="O47">
-        <v>903.8805201599999</v>
+        <v>901.0238206079999</v>
       </c>
       <c r="P47">
-        <v>2862.28831384</v>
+        <v>2853.242098592</v>
       </c>
       <c r="Q47">
-        <v>5752.08831384</v>
+        <v>5743.042098592001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1195449562480999</v>
+        <v>0.1207085122759308</v>
       </c>
       <c r="T47">
-        <v>1.516273918372238</v>
+        <v>1.540197854968379</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.031272773250093</v>
+        <v>7.85667988687509</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08329187662900264</v>
+        <v>0.0831184273215503</v>
       </c>
       <c r="C48">
-        <v>12620.82316571731</v>
+        <v>12415.39360446367</v>
       </c>
       <c r="D48">
-        <v>16728.77916571731</v>
+        <v>16753.13560446367</v>
       </c>
       <c r="E48">
-        <v>241.155999999999</v>
+        <v>470.9419999999991</v>
       </c>
       <c r="F48">
-        <v>10570.156</v>
+        <v>10799.942</v>
       </c>
       <c r="G48">
         <v>6462.2</v>
@@ -5229,28 +5229,28 @@
         <v>4301.8</v>
       </c>
       <c r="M48">
-        <v>547.5340808</v>
+        <v>559.4369955999999</v>
       </c>
       <c r="N48">
-        <v>3754.2659192</v>
+        <v>3742.3630044</v>
       </c>
       <c r="O48">
-        <v>901.0238206079999</v>
+        <v>898.167121056</v>
       </c>
       <c r="P48">
-        <v>2853.242098592</v>
+        <v>2844.195883344</v>
       </c>
       <c r="Q48">
-        <v>5743.042098592001</v>
+        <v>5733.995883344001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1207085122759308</v>
+        <v>0.1219159760783968</v>
       </c>
       <c r="T48">
-        <v>1.540197854968379</v>
+        <v>1.565024581624751</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.85667988687509</v>
+        <v>7.689516485026684</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0831184273215503</v>
+        <v>0.08294497801409795</v>
       </c>
       <c r="C49">
-        <v>12415.39360446367</v>
+        <v>12210.03507064008</v>
       </c>
       <c r="D49">
-        <v>16753.13560446367</v>
+        <v>16777.56307064008</v>
       </c>
       <c r="E49">
-        <v>470.9419999999991</v>
+        <v>700.728000000001</v>
       </c>
       <c r="F49">
-        <v>10799.942</v>
+        <v>11029.728</v>
       </c>
       <c r="G49">
         <v>6462.2</v>
@@ -5311,28 +5311,28 @@
         <v>4301.8</v>
       </c>
       <c r="M49">
-        <v>559.4369955999999</v>
+        <v>571.3399104</v>
       </c>
       <c r="N49">
-        <v>3742.3630044</v>
+        <v>3730.4600896</v>
       </c>
       <c r="O49">
-        <v>898.167121056</v>
+        <v>895.310421504</v>
       </c>
       <c r="P49">
-        <v>2844.195883344</v>
+        <v>2835.149668096</v>
       </c>
       <c r="Q49">
-        <v>5733.995883344001</v>
+        <v>5724.949668096</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1219159760783968</v>
+        <v>0.1231698807963422</v>
       </c>
       <c r="T49">
-        <v>1.565024581624751</v>
+        <v>1.590806182383291</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.689516485026684</v>
+        <v>7.529318224921961</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08294497801409795</v>
+        <v>0.08277152870664559</v>
       </c>
       <c r="C50">
-        <v>12210.03507064008</v>
+        <v>12004.74787539193</v>
       </c>
       <c r="D50">
-        <v>16777.56307064008</v>
+        <v>16802.06187539193</v>
       </c>
       <c r="E50">
-        <v>700.7279999999992</v>
+        <v>930.5139999999992</v>
       </c>
       <c r="F50">
-        <v>11029.728</v>
+        <v>11259.514</v>
       </c>
       <c r="G50">
         <v>6462.2</v>
@@ -5393,28 +5393,28 @@
         <v>4301.8</v>
       </c>
       <c r="M50">
-        <v>571.3399103999999</v>
+        <v>583.2428252</v>
       </c>
       <c r="N50">
-        <v>3730.4600896</v>
+        <v>3718.5571748</v>
       </c>
       <c r="O50">
-        <v>895.310421504</v>
+        <v>892.453721952</v>
       </c>
       <c r="P50">
-        <v>2835.149668096</v>
+        <v>2826.103452848</v>
       </c>
       <c r="Q50">
-        <v>5724.949668096</v>
+        <v>5715.903452848001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1231698807963422</v>
+        <v>0.1244729582483247</v>
       </c>
       <c r="T50">
-        <v>1.590806182383291</v>
+        <v>1.617598826308833</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.529318224921962</v>
+        <v>7.375658669311309</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08277152870664559</v>
+        <v>0.08259807939919325</v>
       </c>
       <c r="C51">
-        <v>12004.74787539193</v>
+        <v>11799.53233168463</v>
       </c>
       <c r="D51">
-        <v>16802.06187539193</v>
+        <v>16826.63233168463</v>
       </c>
       <c r="E51">
-        <v>930.5139999999992</v>
+        <v>1160.299999999999</v>
       </c>
       <c r="F51">
-        <v>11259.514</v>
+        <v>11489.3</v>
       </c>
       <c r="G51">
         <v>6462.2</v>
@@ -5475,28 +5475,28 @@
         <v>4301.8</v>
       </c>
       <c r="M51">
-        <v>583.2428252</v>
+        <v>595.1457399999999</v>
       </c>
       <c r="N51">
-        <v>3718.5571748</v>
+        <v>3706.65426</v>
       </c>
       <c r="O51">
-        <v>892.453721952</v>
+        <v>889.5970224</v>
       </c>
       <c r="P51">
-        <v>2826.103452848</v>
+        <v>2817.0572376</v>
       </c>
       <c r="Q51">
-        <v>5715.903452848001</v>
+        <v>5706.8572376</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1244729582483247</v>
+        <v>0.1258281587983865</v>
       </c>
       <c r="T51">
-        <v>1.617598826308833</v>
+        <v>1.645463175991397</v>
       </c>
       <c r="U51">
         <v>0.0518</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>7.375658669311309</v>
+        <v>7.228145495925084</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08259807939919325</v>
+        <v>0.08242463009174091</v>
       </c>
       <c r="C52">
-        <v>11799.53233168463</v>
+        <v>11594.38875431692</v>
       </c>
       <c r="D52">
-        <v>16826.63233168463</v>
+        <v>16851.27475431692</v>
       </c>
       <c r="E52">
-        <v>1160.299999999999</v>
+        <v>1390.085999999999</v>
       </c>
       <c r="F52">
-        <v>11489.3</v>
+        <v>11719.086</v>
       </c>
       <c r="G52">
         <v>6462.2</v>
@@ -5557,28 +5557,28 @@
         <v>4301.8</v>
       </c>
       <c r="M52">
-        <v>595.1457399999999</v>
+        <v>607.0486547999999</v>
       </c>
       <c r="N52">
-        <v>3706.65426</v>
+        <v>3694.7513452</v>
       </c>
       <c r="O52">
-        <v>889.5970224</v>
+        <v>886.740322848</v>
       </c>
       <c r="P52">
-        <v>2817.0572376</v>
+        <v>2808.011022352001</v>
       </c>
       <c r="Q52">
-        <v>5706.8572376</v>
+        <v>5697.811022352001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1258281587983865</v>
+        <v>0.1272386736566141</v>
       </c>
       <c r="T52">
-        <v>1.645463175991397</v>
+        <v>1.674464846069168</v>
       </c>
       <c r="U52">
         <v>0.0518</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.228145495925084</v>
+        <v>7.086417152867729</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08242463009174091</v>
+        <v>0.08225118078428856</v>
       </c>
       <c r="C53">
-        <v>11594.38875431692</v>
+        <v>11389.31745993431</v>
       </c>
       <c r="D53">
-        <v>16851.27475431692</v>
+        <v>16875.98945993431</v>
       </c>
       <c r="E53">
-        <v>1390.085999999999</v>
+        <v>1619.871999999999</v>
       </c>
       <c r="F53">
-        <v>11719.086</v>
+        <v>11948.872</v>
       </c>
       <c r="G53">
         <v>6462.2</v>
@@ -5639,28 +5639,28 @@
         <v>4301.8</v>
       </c>
       <c r="M53">
-        <v>607.0486547999999</v>
+        <v>618.9515696</v>
       </c>
       <c r="N53">
-        <v>3694.7513452</v>
+        <v>3682.8484304</v>
       </c>
       <c r="O53">
-        <v>886.740322848</v>
+        <v>883.883623296</v>
       </c>
       <c r="P53">
-        <v>2808.011022352001</v>
+        <v>2798.964807104</v>
       </c>
       <c r="Q53">
-        <v>5697.811022352001</v>
+        <v>5688.764807104</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1272386736566141</v>
+        <v>0.1287079599672678</v>
       </c>
       <c r="T53">
-        <v>1.674464846069168</v>
+        <v>1.704674919066845</v>
       </c>
       <c r="U53">
         <v>0.0518</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.086417152867729</v>
+        <v>6.950139899927964</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08225118078428856</v>
+        <v>0.08207773147683621</v>
       </c>
       <c r="C54">
-        <v>11389.31745993431</v>
+        <v>11184.31876704267</v>
       </c>
       <c r="D54">
-        <v>16875.98945993431</v>
+        <v>16900.77676704267</v>
       </c>
       <c r="E54">
-        <v>1619.871999999999</v>
+        <v>1849.657999999999</v>
       </c>
       <c r="F54">
-        <v>11948.872</v>
+        <v>12178.658</v>
       </c>
       <c r="G54">
         <v>6462.2</v>
@@ -5721,28 +5721,28 @@
         <v>4301.8</v>
       </c>
       <c r="M54">
-        <v>618.9515696</v>
+        <v>630.8544843999999</v>
       </c>
       <c r="N54">
-        <v>3682.8484304</v>
+        <v>3670.9455156</v>
       </c>
       <c r="O54">
-        <v>883.883623296</v>
+        <v>881.0269237440001</v>
       </c>
       <c r="P54">
-        <v>2798.964807104</v>
+        <v>2789.918591856</v>
       </c>
       <c r="Q54">
-        <v>5688.764807104</v>
+        <v>5679.718591856001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1287079599672678</v>
+        <v>0.1302397690996515</v>
       </c>
       <c r="T54">
-        <v>1.704674919066845</v>
+        <v>1.736170527085701</v>
       </c>
       <c r="U54">
         <v>0.0518</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.950139899927964</v>
+        <v>6.819005184834984</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08207773147683621</v>
+        <v>0.08260196216938387</v>
       </c>
       <c r="C55">
-        <v>11184.31876704267</v>
+        <v>10879.83752050383</v>
       </c>
       <c r="D55">
-        <v>16900.77676704267</v>
+        <v>16826.08152050383</v>
       </c>
       <c r="E55">
-        <v>1849.657999999999</v>
+        <v>2079.444</v>
       </c>
       <c r="F55">
-        <v>12178.658</v>
+        <v>12408.444</v>
       </c>
       <c r="G55">
         <v>6462.2</v>
@@ -5803,45 +5803,45 @@
         <v>4301.8</v>
       </c>
       <c r="M55">
-        <v>630.8544843999999</v>
+        <v>663.8517539999999</v>
       </c>
       <c r="N55">
-        <v>3670.9455156</v>
+        <v>3637.948246</v>
       </c>
       <c r="O55">
-        <v>881.0269237440001</v>
+        <v>873.10757904</v>
       </c>
       <c r="P55">
-        <v>2789.918591856</v>
+        <v>2764.84066696</v>
       </c>
       <c r="Q55">
-        <v>5679.718591856001</v>
+        <v>5654.64066696</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1302397690996515</v>
+        <v>0.1318381786290954</v>
       </c>
       <c r="T55">
-        <v>1.736170527085701</v>
+        <v>1.769035509366245</v>
       </c>
       <c r="U55">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V55">
         <v>0.24</v>
       </c>
       <c r="W55">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>6.819005184834984</v>
+        <v>6.480061209569389</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08260196216938387</v>
+        <v>0.08244143286193154</v>
       </c>
       <c r="C56">
-        <v>10879.83752050383</v>
+        <v>10672.85438137559</v>
       </c>
       <c r="D56">
-        <v>16826.08152050383</v>
+        <v>16848.88438137558</v>
       </c>
       <c r="E56">
-        <v>2079.444</v>
+        <v>2309.23</v>
       </c>
       <c r="F56">
-        <v>12408.444</v>
+        <v>12638.23</v>
       </c>
       <c r="G56">
         <v>6462.2</v>
@@ -5885,28 +5885,28 @@
         <v>4301.8</v>
       </c>
       <c r="M56">
-        <v>663.8517539999999</v>
+        <v>676.145305</v>
       </c>
       <c r="N56">
-        <v>3637.948246</v>
+        <v>3625.654695</v>
       </c>
       <c r="O56">
-        <v>873.10757904</v>
+        <v>870.1571268</v>
       </c>
       <c r="P56">
-        <v>2764.84066696</v>
+        <v>2755.4975682</v>
       </c>
       <c r="Q56">
-        <v>5654.64066696</v>
+        <v>5645.297568200001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1318381786290954</v>
+        <v>0.1335076285820701</v>
       </c>
       <c r="T56">
-        <v>1.769035509366245</v>
+        <v>1.803361157525925</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.480061209569389</v>
+        <v>6.362241914849945</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08244143286193154</v>
+        <v>0.08228090355447917</v>
       </c>
       <c r="C57">
-        <v>10672.85438137559</v>
+        <v>10465.93313141487</v>
       </c>
       <c r="D57">
-        <v>16848.88438137558</v>
+        <v>16871.74913141486</v>
       </c>
       <c r="E57">
-        <v>2309.23</v>
+        <v>2539.016</v>
       </c>
       <c r="F57">
-        <v>12638.23</v>
+        <v>12868.016</v>
       </c>
       <c r="G57">
         <v>6462.2</v>
@@ -5967,28 +5967,28 @@
         <v>4301.8</v>
       </c>
       <c r="M57">
-        <v>676.145305</v>
+        <v>688.438856</v>
       </c>
       <c r="N57">
-        <v>3625.654695</v>
+        <v>3613.361144</v>
       </c>
       <c r="O57">
-        <v>870.1571268</v>
+        <v>867.2066745600001</v>
       </c>
       <c r="P57">
-        <v>2755.4975682</v>
+        <v>2746.15446944</v>
       </c>
       <c r="Q57">
-        <v>5645.297568200001</v>
+        <v>5635.954469440001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1335076285820701</v>
+        <v>0.1352529626238163</v>
       </c>
       <c r="T57">
-        <v>1.803361157525925</v>
+        <v>1.839247062420136</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.362241914849945</v>
+        <v>6.248630452084768</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08228090355447917</v>
+        <v>0.08212037424702684</v>
       </c>
       <c r="C58">
-        <v>10465.93313141487</v>
+        <v>10259.07402292382</v>
       </c>
       <c r="D58">
-        <v>16871.74913141486</v>
+        <v>16894.67602292382</v>
       </c>
       <c r="E58">
-        <v>2539.016</v>
+        <v>2768.802000000001</v>
       </c>
       <c r="F58">
-        <v>12868.016</v>
+        <v>13097.802</v>
       </c>
       <c r="G58">
         <v>6462.2</v>
@@ -6049,28 +6049,28 @@
         <v>4301.8</v>
       </c>
       <c r="M58">
-        <v>688.438856</v>
+        <v>700.7324070000001</v>
       </c>
       <c r="N58">
-        <v>3613.361144</v>
+        <v>3601.067593</v>
       </c>
       <c r="O58">
-        <v>867.2066745600001</v>
+        <v>864.25622232</v>
       </c>
       <c r="P58">
-        <v>2746.15446944</v>
+        <v>2736.81137068</v>
       </c>
       <c r="Q58">
-        <v>5635.954469440001</v>
+        <v>5626.611370680001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1352529626238163</v>
+        <v>0.1370794749930857</v>
       </c>
       <c r="T58">
-        <v>1.839247062420136</v>
+        <v>1.876802079169892</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.248630452084768</v>
+        <v>6.139005356434157</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08212037424702684</v>
+        <v>0.08195984493957448</v>
       </c>
       <c r="C59">
-        <v>10259.07402292382</v>
+        <v>10052.27730957789</v>
       </c>
       <c r="D59">
-        <v>16894.67602292382</v>
+        <v>16917.66530957789</v>
       </c>
       <c r="E59">
-        <v>2768.802000000001</v>
+        <v>2998.588000000002</v>
       </c>
       <c r="F59">
-        <v>13097.802</v>
+        <v>13327.588</v>
       </c>
       <c r="G59">
         <v>6462.2</v>
@@ -6131,28 +6131,28 @@
         <v>4301.8</v>
       </c>
       <c r="M59">
-        <v>700.7324070000001</v>
+        <v>713.0259580000001</v>
       </c>
       <c r="N59">
-        <v>3601.067593</v>
+        <v>3588.774042</v>
       </c>
       <c r="O59">
-        <v>864.25622232</v>
+        <v>861.30577008</v>
       </c>
       <c r="P59">
-        <v>2736.81137068</v>
+        <v>2727.46827192</v>
       </c>
       <c r="Q59">
-        <v>5626.611370680001</v>
+        <v>5617.26827192</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1370794749930857</v>
+        <v>0.138992964141844</v>
       </c>
       <c r="T59">
-        <v>1.876802079169892</v>
+        <v>1.916145430050588</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.139005356434157</v>
+        <v>6.033160436495637</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08195984493957449</v>
+        <v>0.08179931563212214</v>
       </c>
       <c r="C60">
-        <v>10052.27730957789</v>
+        <v>9845.543246435112</v>
       </c>
       <c r="D60">
-        <v>16917.66530957789</v>
+        <v>16940.71724643511</v>
       </c>
       <c r="E60">
-        <v>2998.587999999998</v>
+        <v>3228.373999999998</v>
       </c>
       <c r="F60">
-        <v>13327.588</v>
+        <v>13557.374</v>
       </c>
       <c r="G60">
         <v>6462.2</v>
@@ -6213,28 +6213,28 @@
         <v>4301.8</v>
       </c>
       <c r="M60">
-        <v>713.0259579999998</v>
+        <v>725.3195089999999</v>
       </c>
       <c r="N60">
-        <v>3588.774042</v>
+        <v>3576.480491</v>
       </c>
       <c r="O60">
-        <v>861.3057700800001</v>
+        <v>858.35531784</v>
       </c>
       <c r="P60">
-        <v>2727.46827192</v>
+        <v>2718.12517316</v>
       </c>
       <c r="Q60">
-        <v>5617.26827192</v>
+        <v>5607.925173160001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.138992964141844</v>
+        <v>0.1409997942246881</v>
       </c>
       <c r="T60">
-        <v>1.916145430050588</v>
+        <v>1.957407968779123</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.033160436495639</v>
+        <v>5.930903479944865</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08179931563212214</v>
+        <v>0.0816387863246698</v>
       </c>
       <c r="C61">
-        <v>9845.543246435112</v>
+        <v>9638.872089945622</v>
       </c>
       <c r="D61">
-        <v>16940.71724643511</v>
+        <v>16963.83208994562</v>
       </c>
       <c r="E61">
-        <v>3228.373999999998</v>
+        <v>3458.159999999998</v>
       </c>
       <c r="F61">
-        <v>13557.374</v>
+        <v>13787.16</v>
       </c>
       <c r="G61">
         <v>6462.2</v>
@@ -6295,28 +6295,28 @@
         <v>4301.8</v>
       </c>
       <c r="M61">
-        <v>725.3195089999999</v>
+        <v>737.6130599999999</v>
       </c>
       <c r="N61">
-        <v>3576.480491</v>
+        <v>3564.186940000001</v>
       </c>
       <c r="O61">
-        <v>858.35531784</v>
+        <v>855.4048656000001</v>
       </c>
       <c r="P61">
-        <v>2718.12517316</v>
+        <v>2708.782074400001</v>
       </c>
       <c r="Q61">
-        <v>5607.925173160001</v>
+        <v>5598.582074400001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1409997942246881</v>
+        <v>0.1431069658116745</v>
       </c>
       <c r="T61">
-        <v>1.957407968779123</v>
+        <v>2.000733634444085</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.930903479944865</v>
+        <v>5.832055088612451</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0816387863246698</v>
+        <v>0.08147825701721745</v>
       </c>
       <c r="C62">
-        <v>9638.872089945622</v>
+        <v>9432.264097961097</v>
       </c>
       <c r="D62">
-        <v>16963.83208994562</v>
+        <v>16987.01009796109</v>
       </c>
       <c r="E62">
-        <v>3458.159999999998</v>
+        <v>3687.945999999998</v>
       </c>
       <c r="F62">
-        <v>13787.16</v>
+        <v>14016.946</v>
       </c>
       <c r="G62">
         <v>6462.2</v>
@@ -6377,28 +6377,28 @@
         <v>4301.8</v>
       </c>
       <c r="M62">
-        <v>737.6130599999999</v>
+        <v>749.9066109999999</v>
       </c>
       <c r="N62">
-        <v>3564.186940000001</v>
+        <v>3551.893389</v>
       </c>
       <c r="O62">
-        <v>855.4048656000001</v>
+        <v>852.45441336</v>
       </c>
       <c r="P62">
-        <v>2708.782074400001</v>
+        <v>2699.438975640001</v>
       </c>
       <c r="Q62">
-        <v>5598.582074400001</v>
+        <v>5589.238975640001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1431069658116745</v>
+        <v>0.1453221974800447</v>
       </c>
       <c r="T62">
-        <v>2.000733634444085</v>
+        <v>2.046281129117506</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.832055088612451</v>
+        <v>5.736447628143394</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08147825701721745</v>
+        <v>0.08131772770976511</v>
       </c>
       <c r="C63">
-        <v>9432.264097961097</v>
+        <v>9225.719529744385</v>
       </c>
       <c r="D63">
-        <v>16987.01009796109</v>
+        <v>17010.25152974438</v>
       </c>
       <c r="E63">
-        <v>3687.945999999998</v>
+        <v>3917.731999999998</v>
       </c>
       <c r="F63">
-        <v>14016.946</v>
+        <v>14246.732</v>
       </c>
       <c r="G63">
         <v>6462.2</v>
@@ -6459,28 +6459,28 @@
         <v>4301.8</v>
       </c>
       <c r="M63">
-        <v>749.9066109999999</v>
+        <v>762.2001619999999</v>
       </c>
       <c r="N63">
-        <v>3551.893389</v>
+        <v>3539.599838</v>
       </c>
       <c r="O63">
-        <v>852.45441336</v>
+        <v>849.50396112</v>
       </c>
       <c r="P63">
-        <v>2699.438975640001</v>
+        <v>2690.09587688</v>
       </c>
       <c r="Q63">
-        <v>5589.238975640001</v>
+        <v>5579.89587688</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1453221974800447</v>
+        <v>0.1476540202888555</v>
       </c>
       <c r="T63">
-        <v>2.046281129117506</v>
+        <v>2.094225860352688</v>
       </c>
       <c r="U63">
         <v>0.0535</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.736447628143394</v>
+        <v>5.643924279302372</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08131772770976511</v>
+        <v>0.08154023840231275</v>
       </c>
       <c r="C64">
-        <v>9225.719529744385</v>
+        <v>8963.735419483659</v>
       </c>
       <c r="D64">
-        <v>17010.25152974438</v>
+        <v>16978.05341948366</v>
       </c>
       <c r="E64">
-        <v>3917.731999999998</v>
+        <v>4147.518</v>
       </c>
       <c r="F64">
-        <v>14246.732</v>
+        <v>14476.518</v>
       </c>
       <c r="G64">
         <v>6462.2</v>
@@ -6541,45 +6541,45 @@
         <v>4301.8</v>
       </c>
       <c r="M64">
-        <v>762.2001619999999</v>
+        <v>786.0749274</v>
       </c>
       <c r="N64">
-        <v>3539.599838</v>
+        <v>3515.7250726</v>
       </c>
       <c r="O64">
-        <v>849.50396112</v>
+        <v>843.774017424</v>
       </c>
       <c r="P64">
-        <v>2690.09587688</v>
+        <v>2671.951055176</v>
       </c>
       <c r="Q64">
-        <v>5579.89587688</v>
+        <v>5561.751055176001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1476540202888555</v>
+        <v>0.1501118875738182</v>
       </c>
       <c r="T64">
-        <v>2.094225860352688</v>
+        <v>2.144762198681661</v>
       </c>
       <c r="U64">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V64">
         <v>0.24</v>
       </c>
       <c r="W64">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y64">
-        <v>5.643924279302372</v>
+        <v>5.472506309581094</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08154023840231275</v>
+        <v>0.08138578909486041</v>
       </c>
       <c r="C65">
-        <v>8963.735419483659</v>
+        <v>8756.285841580542</v>
       </c>
       <c r="D65">
-        <v>16978.05341948366</v>
+        <v>17000.38984158054</v>
       </c>
       <c r="E65">
-        <v>4147.518</v>
+        <v>4377.304</v>
       </c>
       <c r="F65">
-        <v>14476.518</v>
+        <v>14706.304</v>
       </c>
       <c r="G65">
         <v>6462.2</v>
@@ -6623,28 +6623,28 @@
         <v>4301.8</v>
       </c>
       <c r="M65">
-        <v>786.0749274</v>
+        <v>798.5523072</v>
       </c>
       <c r="N65">
-        <v>3515.7250726</v>
+        <v>3503.2476928</v>
       </c>
       <c r="O65">
-        <v>843.774017424</v>
+        <v>840.779446272</v>
       </c>
       <c r="P65">
-        <v>2671.951055176</v>
+        <v>2662.468246528</v>
       </c>
       <c r="Q65">
-        <v>5561.751055176001</v>
+        <v>5552.268246528</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1501118875738182</v>
+        <v>0.1527063030412789</v>
       </c>
       <c r="T65">
-        <v>2.144762198681661</v>
+        <v>2.198106111362245</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.472506309581094</v>
+        <v>5.38699839849389</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08138578909486041</v>
+        <v>0.08123133978740807</v>
       </c>
       <c r="C66">
-        <v>8756.285841580542</v>
+        <v>8548.895112943679</v>
       </c>
       <c r="D66">
-        <v>17000.38984158054</v>
+        <v>17022.78511294368</v>
       </c>
       <c r="E66">
-        <v>4377.304</v>
+        <v>4607.09</v>
       </c>
       <c r="F66">
-        <v>14706.304</v>
+        <v>14936.09</v>
       </c>
       <c r="G66">
         <v>6462.2</v>
@@ -6705,28 +6705,28 @@
         <v>4301.8</v>
       </c>
       <c r="M66">
-        <v>798.5523072</v>
+        <v>811.029687</v>
       </c>
       <c r="N66">
-        <v>3503.2476928</v>
+        <v>3490.770313</v>
       </c>
       <c r="O66">
-        <v>840.779446272</v>
+        <v>837.7848751199999</v>
       </c>
       <c r="P66">
-        <v>2662.468246528</v>
+        <v>2652.98543788</v>
       </c>
       <c r="Q66">
-        <v>5552.268246528</v>
+        <v>5542.78543788</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1527063030412789</v>
+        <v>0.1554489708211659</v>
       </c>
       <c r="T66">
-        <v>2.198106111362245</v>
+        <v>2.254498247624577</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.38699839849389</v>
+        <v>5.304121500055522</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08123133978740807</v>
+        <v>0.08107689047995573</v>
       </c>
       <c r="C67">
-        <v>8548.895112943679</v>
+        <v>8341.563466453106</v>
       </c>
       <c r="D67">
-        <v>17022.78511294368</v>
+        <v>17045.23946645311</v>
       </c>
       <c r="E67">
-        <v>4607.09</v>
+        <v>4836.876</v>
       </c>
       <c r="F67">
-        <v>14936.09</v>
+        <v>15165.876</v>
       </c>
       <c r="G67">
         <v>6462.2</v>
@@ -6787,28 +6787,28 @@
         <v>4301.8</v>
       </c>
       <c r="M67">
-        <v>811.029687</v>
+        <v>823.5070668000001</v>
       </c>
       <c r="N67">
-        <v>3490.770313</v>
+        <v>3478.2929332</v>
       </c>
       <c r="O67">
-        <v>837.7848751199999</v>
+        <v>834.7903039680001</v>
       </c>
       <c r="P67">
-        <v>2652.98543788</v>
+        <v>2643.502629232</v>
       </c>
       <c r="Q67">
-        <v>5542.78543788</v>
+        <v>5533.302629232001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1554489708211659</v>
+        <v>0.1583529719998698</v>
       </c>
       <c r="T67">
-        <v>2.254498247624577</v>
+        <v>2.314207568372928</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.304121500055522</v>
+        <v>5.223756022781953</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08107689047995573</v>
+        <v>0.08092244117250338</v>
       </c>
       <c r="C68">
-        <v>8341.563466453106</v>
+        <v>8134.291136219214</v>
       </c>
       <c r="D68">
-        <v>17045.23946645311</v>
+        <v>17067.75313621921</v>
       </c>
       <c r="E68">
-        <v>4836.876</v>
+        <v>5066.662</v>
       </c>
       <c r="F68">
-        <v>15165.876</v>
+        <v>15395.662</v>
       </c>
       <c r="G68">
         <v>6462.2</v>
@@ -6869,28 +6869,28 @@
         <v>4301.8</v>
       </c>
       <c r="M68">
-        <v>823.5070668000001</v>
+        <v>835.9844466000001</v>
       </c>
       <c r="N68">
-        <v>3478.2929332</v>
+        <v>3465.8155534</v>
       </c>
       <c r="O68">
-        <v>834.7903039680001</v>
+        <v>831.7957328160001</v>
       </c>
       <c r="P68">
-        <v>2643.502629232</v>
+        <v>2634.019820584</v>
       </c>
       <c r="Q68">
-        <v>5533.302629232001</v>
+        <v>5523.819820584</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1583529719998698</v>
+        <v>0.1614329732500103</v>
       </c>
       <c r="T68">
-        <v>2.314207568372928</v>
+        <v>2.3775356358333</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.223756022781953</v>
+        <v>5.145789514979237</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08092244117250338</v>
+        <v>0.08076799186505104</v>
       </c>
       <c r="C69">
-        <v>8134.291136219214</v>
+        <v>7927.078357590912</v>
       </c>
       <c r="D69">
-        <v>17067.75313621921</v>
+        <v>17090.32635759091</v>
       </c>
       <c r="E69">
-        <v>5066.662</v>
+        <v>5296.448</v>
       </c>
       <c r="F69">
-        <v>15395.662</v>
+        <v>15625.448</v>
       </c>
       <c r="G69">
         <v>6462.2</v>
@@ -6951,28 +6951,28 @@
         <v>4301.8</v>
       </c>
       <c r="M69">
-        <v>835.9844466000001</v>
+        <v>848.4618264000001</v>
       </c>
       <c r="N69">
-        <v>3465.8155534</v>
+        <v>3453.3381736</v>
       </c>
       <c r="O69">
-        <v>831.7957328160001</v>
+        <v>828.801161664</v>
       </c>
       <c r="P69">
-        <v>2634.019820584</v>
+        <v>2624.537011936</v>
       </c>
       <c r="Q69">
-        <v>5523.819820584</v>
+        <v>5514.337011936001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1614329732500103</v>
+        <v>0.1647054745782845</v>
       </c>
       <c r="T69">
-        <v>2.3775356358333</v>
+        <v>2.444821707509945</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.145789514979237</v>
+        <v>5.070116139758954</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08076799186505104</v>
+        <v>0.08061354255759869</v>
       </c>
       <c r="C70">
-        <v>7927.078357590912</v>
+        <v>7719.925367163811</v>
       </c>
       <c r="D70">
-        <v>17090.32635759091</v>
+        <v>17112.95936716381</v>
       </c>
       <c r="E70">
-        <v>5296.448</v>
+        <v>5526.234</v>
       </c>
       <c r="F70">
-        <v>15625.448</v>
+        <v>15855.234</v>
       </c>
       <c r="G70">
         <v>6462.2</v>
@@ -7033,28 +7033,28 @@
         <v>4301.8</v>
       </c>
       <c r="M70">
-        <v>848.4618264000001</v>
+        <v>860.9392062000001</v>
       </c>
       <c r="N70">
-        <v>3453.3381736</v>
+        <v>3440.8607938</v>
       </c>
       <c r="O70">
-        <v>828.801161664</v>
+        <v>825.806590512</v>
       </c>
       <c r="P70">
-        <v>2624.537011936</v>
+        <v>2615.054203288</v>
       </c>
       <c r="Q70">
-        <v>5514.337011936001</v>
+        <v>5504.854203288</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1647054745782845</v>
+        <v>0.1681891050245119</v>
       </c>
       <c r="T70">
-        <v>2.444821707509945</v>
+        <v>2.516448816068956</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.070116139758954</v>
+        <v>4.996636195704476</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08061354255759869</v>
+        <v>0.08045909325014634</v>
       </c>
       <c r="C71">
-        <v>7719.925367163811</v>
+        <v>7512.832402788485</v>
       </c>
       <c r="D71">
-        <v>17112.95936716381</v>
+        <v>17135.65240278848</v>
       </c>
       <c r="E71">
-        <v>5526.234</v>
+        <v>5756.02</v>
       </c>
       <c r="F71">
-        <v>15855.234</v>
+        <v>16085.02</v>
       </c>
       <c r="G71">
         <v>6462.2</v>
@@ -7115,28 +7115,28 @@
         <v>4301.8</v>
       </c>
       <c r="M71">
-        <v>860.9392062000001</v>
+        <v>873.4165860000001</v>
       </c>
       <c r="N71">
-        <v>3440.8607938</v>
+        <v>3428.383414</v>
       </c>
       <c r="O71">
-        <v>825.806590512</v>
+        <v>822.8120193599999</v>
       </c>
       <c r="P71">
-        <v>2615.054203288</v>
+        <v>2605.57139464</v>
       </c>
       <c r="Q71">
-        <v>5504.854203288</v>
+        <v>5495.37139464</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1681891050245119</v>
+        <v>0.1719049775004878</v>
       </c>
       <c r="T71">
-        <v>2.516448816068956</v>
+        <v>2.592851065198566</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.996636195704476</v>
+        <v>4.925255678622984</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08045909325014634</v>
+        <v>0.08030464394269402</v>
       </c>
       <c r="C72">
-        <v>7512.832402788485</v>
+        <v>7305.799703578825</v>
       </c>
       <c r="D72">
-        <v>17135.65240278848</v>
+        <v>17158.40570357882</v>
       </c>
       <c r="E72">
-        <v>5756.02</v>
+        <v>5985.806</v>
       </c>
       <c r="F72">
-        <v>16085.02</v>
+        <v>16314.806</v>
       </c>
       <c r="G72">
         <v>6462.2</v>
@@ -7197,28 +7197,28 @@
         <v>4301.8</v>
       </c>
       <c r="M72">
-        <v>873.4165860000001</v>
+        <v>885.8939658</v>
       </c>
       <c r="N72">
-        <v>3428.383414</v>
+        <v>3415.9060342</v>
       </c>
       <c r="O72">
-        <v>822.8120193599999</v>
+        <v>819.817448208</v>
       </c>
       <c r="P72">
-        <v>2605.57139464</v>
+        <v>2596.088585992</v>
       </c>
       <c r="Q72">
-        <v>5495.37139464</v>
+        <v>5485.888585992001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1719049775004878</v>
+        <v>0.1758771170437725</v>
       </c>
       <c r="T72">
-        <v>2.592851065198566</v>
+        <v>2.674522434957805</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.925255678622984</v>
+        <v>4.85588588033252</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08030464394269402</v>
+        <v>0.08015019463524166</v>
       </c>
       <c r="C73">
-        <v>7305.799703578827</v>
+        <v>7098.827509920418</v>
       </c>
       <c r="D73">
-        <v>17158.40570357882</v>
+        <v>17181.21950992041</v>
       </c>
       <c r="E73">
-        <v>5985.805999999999</v>
+        <v>6215.591999999997</v>
       </c>
       <c r="F73">
-        <v>16314.806</v>
+        <v>16544.592</v>
       </c>
       <c r="G73">
         <v>6462.2</v>
@@ -7279,28 +7279,28 @@
         <v>4301.8</v>
       </c>
       <c r="M73">
-        <v>885.8939657999999</v>
+        <v>898.3713455999998</v>
       </c>
       <c r="N73">
-        <v>3415.9060342</v>
+        <v>3403.428654400001</v>
       </c>
       <c r="O73">
-        <v>819.817448208</v>
+        <v>816.8228770560002</v>
       </c>
       <c r="P73">
-        <v>2596.088585992</v>
+        <v>2586.605777344001</v>
       </c>
       <c r="Q73">
-        <v>5485.888585992001</v>
+        <v>5476.405777344001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1758771170437724</v>
+        <v>0.1801329808401488</v>
       </c>
       <c r="T73">
-        <v>2.674522434957804</v>
+        <v>2.762027473985559</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.85588588033252</v>
+        <v>4.788443020883458</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08015019463524166</v>
+        <v>0.07999574532778932</v>
       </c>
       <c r="C74">
-        <v>7098.827509920418</v>
+        <v>6891.916063479024</v>
       </c>
       <c r="D74">
-        <v>17181.21950992041</v>
+        <v>17204.09406347902</v>
       </c>
       <c r="E74">
-        <v>6215.591999999997</v>
+        <v>6445.377999999997</v>
       </c>
       <c r="F74">
-        <v>16544.592</v>
+        <v>16774.378</v>
       </c>
       <c r="G74">
         <v>6462.2</v>
@@ -7361,28 +7361,28 @@
         <v>4301.8</v>
       </c>
       <c r="M74">
-        <v>898.3713455999998</v>
+        <v>910.8487253999998</v>
       </c>
       <c r="N74">
-        <v>3403.428654400001</v>
+        <v>3390.9512746</v>
       </c>
       <c r="O74">
-        <v>816.8228770560002</v>
+        <v>813.8283059040001</v>
       </c>
       <c r="P74">
-        <v>2586.605777344001</v>
+        <v>2577.122968696</v>
       </c>
       <c r="Q74">
-        <v>5476.405777344001</v>
+        <v>5466.922968696001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1801329808401488</v>
+        <v>0.1847040938066271</v>
       </c>
       <c r="T74">
-        <v>2.762027473985559</v>
+        <v>2.856014367756112</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.788443020883458</v>
+        <v>4.722847911008342</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07999574532778932</v>
+        <v>0.07984129602033696</v>
       </c>
       <c r="C75">
-        <v>6891.916063479024</v>
+        <v>6685.065607209097</v>
       </c>
       <c r="D75">
-        <v>17204.09406347902</v>
+        <v>17227.02960720909</v>
       </c>
       <c r="E75">
-        <v>6445.377999999997</v>
+        <v>6675.163999999997</v>
       </c>
       <c r="F75">
-        <v>16774.378</v>
+        <v>17004.164</v>
       </c>
       <c r="G75">
         <v>6462.2</v>
@@ -7443,28 +7443,28 @@
         <v>4301.8</v>
       </c>
       <c r="M75">
-        <v>910.8487253999998</v>
+        <v>923.3261051999998</v>
       </c>
       <c r="N75">
-        <v>3390.9512746</v>
+        <v>3378.4738948</v>
       </c>
       <c r="O75">
-        <v>813.8283059040001</v>
+        <v>810.8337347520001</v>
       </c>
       <c r="P75">
-        <v>2577.122968696</v>
+        <v>2567.640160048</v>
       </c>
       <c r="Q75">
-        <v>5466.922968696001</v>
+        <v>5457.440160048001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1847040938066271</v>
+        <v>0.1896268308474499</v>
       </c>
       <c r="T75">
-        <v>2.856014367756112</v>
+        <v>2.957231022585937</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.722847911008342</v>
+        <v>4.659025641940662</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07984129602033696</v>
+        <v>0.07968684671288462</v>
       </c>
       <c r="C76">
-        <v>6685.065607209097</v>
+        <v>6478.276385362398</v>
       </c>
       <c r="D76">
-        <v>17227.02960720909</v>
+        <v>17250.02638536239</v>
       </c>
       <c r="E76">
-        <v>6675.163999999997</v>
+        <v>6904.949999999997</v>
       </c>
       <c r="F76">
-        <v>17004.164</v>
+        <v>17233.95</v>
       </c>
       <c r="G76">
         <v>6462.2</v>
@@ -7525,28 +7525,28 @@
         <v>4301.8</v>
       </c>
       <c r="M76">
-        <v>923.3261051999998</v>
+        <v>935.8034849999999</v>
       </c>
       <c r="N76">
-        <v>3378.4738948</v>
+        <v>3365.996515</v>
       </c>
       <c r="O76">
-        <v>810.8337347520001</v>
+        <v>807.8391636</v>
       </c>
       <c r="P76">
-        <v>2567.640160048</v>
+        <v>2558.1573514</v>
       </c>
       <c r="Q76">
-        <v>5457.440160048001</v>
+        <v>5447.9573514</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1896268308474499</v>
+        <v>0.1949433868515385</v>
       </c>
       <c r="T76">
-        <v>2.957231022585937</v>
+        <v>3.066545009802149</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.659025641940662</v>
+        <v>4.596905300048119</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07968684671288462</v>
+        <v>0.07953239740543228</v>
       </c>
       <c r="C77">
-        <v>6478.276385362398</v>
+        <v>6271.548643496666</v>
       </c>
       <c r="D77">
-        <v>17250.02638536239</v>
+        <v>17273.08464349667</v>
       </c>
       <c r="E77">
-        <v>6904.949999999997</v>
+        <v>7134.736000000001</v>
       </c>
       <c r="F77">
-        <v>17233.95</v>
+        <v>17463.736</v>
       </c>
       <c r="G77">
         <v>6462.2</v>
@@ -7607,28 +7607,28 @@
         <v>4301.8</v>
       </c>
       <c r="M77">
-        <v>935.8034849999999</v>
+        <v>948.2808648</v>
       </c>
       <c r="N77">
-        <v>3365.996515</v>
+        <v>3353.5191352</v>
       </c>
       <c r="O77">
-        <v>807.8391636</v>
+        <v>804.844592448</v>
       </c>
       <c r="P77">
-        <v>2558.1573514</v>
+        <v>2548.674542752</v>
       </c>
       <c r="Q77">
-        <v>5447.9573514</v>
+        <v>5438.474542752</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1949433868515385</v>
+        <v>0.2007029891893012</v>
       </c>
       <c r="T77">
-        <v>3.066545009802149</v>
+        <v>3.184968495953045</v>
       </c>
       <c r="U77">
         <v>0.0543</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.596905300048119</v>
+        <v>4.536419703994854</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07953239740543228</v>
+        <v>0.07937794809797993</v>
       </c>
       <c r="C78">
-        <v>6271.548643496666</v>
+        <v>6064.882628484349</v>
       </c>
       <c r="D78">
-        <v>17273.08464349667</v>
+        <v>17296.20462848435</v>
       </c>
       <c r="E78">
-        <v>7134.736000000001</v>
+        <v>7364.522000000001</v>
       </c>
       <c r="F78">
-        <v>17463.736</v>
+        <v>17693.522</v>
       </c>
       <c r="G78">
         <v>6462.2</v>
@@ -7689,28 +7689,28 @@
         <v>4301.8</v>
       </c>
       <c r="M78">
-        <v>948.2808648</v>
+        <v>960.7582446</v>
       </c>
       <c r="N78">
-        <v>3353.5191352</v>
+        <v>3341.0417554</v>
       </c>
       <c r="O78">
-        <v>804.844592448</v>
+        <v>801.850021296</v>
       </c>
       <c r="P78">
-        <v>2548.674542752</v>
+        <v>2539.191734104</v>
       </c>
       <c r="Q78">
-        <v>5438.474542752</v>
+        <v>5428.991734104</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2007029891893012</v>
+        <v>0.2069634265129562</v>
       </c>
       <c r="T78">
-        <v>3.184968495953045</v>
+        <v>3.313689676551845</v>
       </c>
       <c r="U78">
         <v>0.0543</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.536419703994854</v>
+        <v>4.477505162384531</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07937794809797993</v>
+        <v>0.07922349879052758</v>
       </c>
       <c r="C79">
-        <v>6064.882628484349</v>
+        <v>5858.278588521422</v>
       </c>
       <c r="D79">
-        <v>17296.20462848435</v>
+        <v>17319.38658852142</v>
       </c>
       <c r="E79">
-        <v>7364.522000000001</v>
+        <v>7594.308000000001</v>
       </c>
       <c r="F79">
-        <v>17693.522</v>
+        <v>17923.308</v>
       </c>
       <c r="G79">
         <v>6462.2</v>
@@ -7771,28 +7771,28 @@
         <v>4301.8</v>
       </c>
       <c r="M79">
-        <v>960.7582446</v>
+        <v>973.2356244000001</v>
       </c>
       <c r="N79">
-        <v>3341.0417554</v>
+        <v>3328.5643756</v>
       </c>
       <c r="O79">
-        <v>801.850021296</v>
+        <v>798.855450144</v>
       </c>
       <c r="P79">
-        <v>2539.191734104</v>
+        <v>2529.708925456</v>
       </c>
       <c r="Q79">
-        <v>5428.991734104</v>
+        <v>5419.508925456001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2069634265129562</v>
+        <v>0.2137929945023981</v>
       </c>
       <c r="T79">
-        <v>3.313689676551845</v>
+        <v>3.454112782659627</v>
       </c>
       <c r="U79">
         <v>0.0543</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.477505162384531</v>
+        <v>4.420101250046267</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07922349879052758</v>
+        <v>0.07906904948307525</v>
       </c>
       <c r="C80">
-        <v>5858.278588521422</v>
+        <v>5651.736773136261</v>
       </c>
       <c r="D80">
-        <v>17319.38658852142</v>
+        <v>17342.63077313626</v>
       </c>
       <c r="E80">
-        <v>7594.308000000001</v>
+        <v>7824.094000000001</v>
       </c>
       <c r="F80">
-        <v>17923.308</v>
+        <v>18153.094</v>
       </c>
       <c r="G80">
         <v>6462.2</v>
@@ -7853,28 +7853,28 @@
         <v>4301.8</v>
       </c>
       <c r="M80">
-        <v>973.2356244000001</v>
+        <v>985.7130042000001</v>
       </c>
       <c r="N80">
-        <v>3328.5643756</v>
+        <v>3316.0869958</v>
       </c>
       <c r="O80">
-        <v>798.855450144</v>
+        <v>795.860878992</v>
       </c>
       <c r="P80">
-        <v>2529.708925456</v>
+        <v>2520.226116808</v>
       </c>
       <c r="Q80">
-        <v>5419.508925456001</v>
+        <v>5410.026116808001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2137929945023981</v>
+        <v>0.2212729975384536</v>
       </c>
       <c r="T80">
-        <v>3.454112782659627</v>
+        <v>3.607909517920532</v>
       </c>
       <c r="U80">
         <v>0.0543</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.420101250046267</v>
+        <v>4.364150601311505</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07906904948307525</v>
+        <v>0.07891460017562289</v>
       </c>
       <c r="C81">
-        <v>5651.736773136261</v>
+        <v>5445.257433198607</v>
       </c>
       <c r="D81">
-        <v>17342.63077313626</v>
+        <v>17365.93743319861</v>
       </c>
       <c r="E81">
-        <v>7824.094000000001</v>
+        <v>8053.880000000001</v>
       </c>
       <c r="F81">
-        <v>18153.094</v>
+        <v>18382.88</v>
       </c>
       <c r="G81">
         <v>6462.2</v>
@@ -7935,28 +7935,28 @@
         <v>4301.8</v>
       </c>
       <c r="M81">
-        <v>985.7130042000001</v>
+        <v>998.1903840000001</v>
       </c>
       <c r="N81">
-        <v>3316.0869958</v>
+        <v>3303.609616</v>
       </c>
       <c r="O81">
-        <v>795.860878992</v>
+        <v>792.86630784</v>
       </c>
       <c r="P81">
-        <v>2520.226116808</v>
+        <v>2510.74330816</v>
       </c>
       <c r="Q81">
-        <v>5410.026116808001</v>
+        <v>5400.54330816</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2212729975384536</v>
+        <v>0.2295010008781145</v>
       </c>
       <c r="T81">
-        <v>3.607909517920532</v>
+        <v>3.777085926707526</v>
       </c>
       <c r="U81">
         <v>0.0543</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.364150601311505</v>
+        <v>4.309598718795111</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07891460017562289</v>
+        <v>0.07876015086817055</v>
       </c>
       <c r="C82">
-        <v>5445.257433198607</v>
+        <v>5238.840820928584</v>
       </c>
       <c r="D82">
-        <v>17365.93743319861</v>
+        <v>17389.30682092858</v>
       </c>
       <c r="E82">
-        <v>8053.880000000001</v>
+        <v>8283.666000000001</v>
       </c>
       <c r="F82">
-        <v>18382.88</v>
+        <v>18612.666</v>
       </c>
       <c r="G82">
         <v>6462.2</v>
@@ -8017,28 +8017,28 @@
         <v>4301.8</v>
       </c>
       <c r="M82">
-        <v>998.1903840000001</v>
+        <v>1010.6677638</v>
       </c>
       <c r="N82">
-        <v>3303.609616</v>
+        <v>3291.1322362</v>
       </c>
       <c r="O82">
-        <v>792.86630784</v>
+        <v>789.8717366879999</v>
       </c>
       <c r="P82">
-        <v>2510.74330816</v>
+        <v>2501.260499512</v>
       </c>
       <c r="Q82">
-        <v>5400.54330816</v>
+        <v>5391.060499512</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2295010008781145</v>
+        <v>0.2385951098324766</v>
       </c>
       <c r="T82">
-        <v>3.777085926707526</v>
+        <v>3.964070378524731</v>
       </c>
       <c r="U82">
         <v>0.0543</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.309598718795111</v>
+        <v>4.25639379634085</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07876015086817055</v>
+        <v>0.07922890156071821</v>
       </c>
       <c r="C83">
-        <v>5238.840820928584</v>
+        <v>4938.322614727334</v>
       </c>
       <c r="D83">
-        <v>17389.30682092858</v>
+        <v>17318.57461472733</v>
       </c>
       <c r="E83">
-        <v>8283.666000000001</v>
+        <v>8513.452000000001</v>
       </c>
       <c r="F83">
-        <v>18612.666</v>
+        <v>18842.452</v>
       </c>
       <c r="G83">
         <v>6462.2</v>
@@ -8099,45 +8099,45 @@
         <v>4301.8</v>
       </c>
       <c r="M83">
-        <v>1010.6677638</v>
+        <v>1041.9875956</v>
       </c>
       <c r="N83">
-        <v>3291.1322362</v>
+        <v>3259.8124044</v>
       </c>
       <c r="O83">
-        <v>789.8717366879999</v>
+        <v>782.3549770560001</v>
       </c>
       <c r="P83">
-        <v>2501.260499512</v>
+        <v>2477.457427344</v>
       </c>
       <c r="Q83">
-        <v>5391.060499512</v>
+        <v>5367.257427344</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2385951098324766</v>
+        <v>0.2486996753373234</v>
       </c>
       <c r="T83">
-        <v>3.964070378524731</v>
+        <v>4.171830880543847</v>
       </c>
       <c r="U83">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V83">
         <v>0.24</v>
       </c>
       <c r="W83">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y83">
-        <v>4.25639379634085</v>
+        <v>4.128456056641371</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07922890156071821</v>
+        <v>0.07908205225326587</v>
       </c>
       <c r="C84">
-        <v>4938.322614727334</v>
+        <v>4730.633488006755</v>
       </c>
       <c r="D84">
-        <v>17318.57461472733</v>
+        <v>17340.67148800676</v>
       </c>
       <c r="E84">
-        <v>8513.452000000001</v>
+        <v>8743.238000000001</v>
       </c>
       <c r="F84">
-        <v>18842.452</v>
+        <v>19072.238</v>
       </c>
       <c r="G84">
         <v>6462.2</v>
@@ -8181,28 +8181,28 @@
         <v>4301.8</v>
       </c>
       <c r="M84">
-        <v>1041.9875956</v>
+        <v>1054.6947614</v>
       </c>
       <c r="N84">
-        <v>3259.8124044</v>
+        <v>3247.1052386</v>
       </c>
       <c r="O84">
-        <v>782.3549770560001</v>
+        <v>779.305257264</v>
       </c>
       <c r="P84">
-        <v>2477.457427344</v>
+        <v>2467.799981336</v>
       </c>
       <c r="Q84">
-        <v>5367.257427344</v>
+        <v>5357.599981336</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2486996753373234</v>
+        <v>0.2599930132545051</v>
       </c>
       <c r="T84">
-        <v>4.171830880543847</v>
+        <v>4.404033794565212</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.128456056641371</v>
+        <v>4.078715622224006</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07908205225326587</v>
+        <v>0.07893520294581352</v>
       </c>
       <c r="C85">
-        <v>4730.633488006755</v>
+        <v>4523.000820389123</v>
       </c>
       <c r="D85">
-        <v>17340.67148800676</v>
+        <v>17362.82482038912</v>
       </c>
       <c r="E85">
-        <v>8743.238000000001</v>
+        <v>8973.024000000001</v>
       </c>
       <c r="F85">
-        <v>19072.238</v>
+        <v>19302.024</v>
       </c>
       <c r="G85">
         <v>6462.2</v>
@@ -8263,28 +8263,28 @@
         <v>4301.8</v>
       </c>
       <c r="M85">
-        <v>1054.6947614</v>
+        <v>1067.4019272</v>
       </c>
       <c r="N85">
-        <v>3247.1052386</v>
+        <v>3234.3980728</v>
       </c>
       <c r="O85">
-        <v>779.305257264</v>
+        <v>776.255537472</v>
       </c>
       <c r="P85">
-        <v>2467.799981336</v>
+        <v>2458.142535328</v>
       </c>
       <c r="Q85">
-        <v>5357.599981336</v>
+        <v>5347.942535328</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2599930132545051</v>
+        <v>0.2726980184113346</v>
       </c>
       <c r="T85">
-        <v>4.404033794565212</v>
+        <v>4.665262072839248</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.078715622224006</v>
+        <v>4.030159483864196</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07893520294581352</v>
+        <v>0.07878835363836117</v>
       </c>
       <c r="C86">
-        <v>4523.000820389127</v>
+        <v>4315.424828536852</v>
       </c>
       <c r="D86">
-        <v>17362.82482038912</v>
+        <v>17385.03482853685</v>
       </c>
       <c r="E86">
-        <v>8973.023999999998</v>
+        <v>9202.809999999998</v>
       </c>
       <c r="F86">
-        <v>19302.024</v>
+        <v>19531.81</v>
       </c>
       <c r="G86">
         <v>6462.2</v>
@@ -8345,28 +8345,28 @@
         <v>4301.8</v>
       </c>
       <c r="M86">
-        <v>1067.4019272</v>
+        <v>1080.109093</v>
       </c>
       <c r="N86">
-        <v>3234.398072800001</v>
+        <v>3221.690907</v>
       </c>
       <c r="O86">
-        <v>776.2555374720001</v>
+        <v>773.20581768</v>
       </c>
       <c r="P86">
-        <v>2458.142535328001</v>
+        <v>2448.48508932</v>
       </c>
       <c r="Q86">
-        <v>5347.942535328</v>
+        <v>5338.28508932</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2726980184113345</v>
+        <v>0.2870970242557411</v>
       </c>
       <c r="T86">
-        <v>4.665262072839245</v>
+        <v>4.961320788216486</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.030159483864197</v>
+        <v>3.982745842877559</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07878835363836117</v>
+        <v>0.07864150433090883</v>
       </c>
       <c r="C87">
-        <v>4315.424828536852</v>
+        <v>4107.905730222352</v>
       </c>
       <c r="D87">
-        <v>17385.03482853685</v>
+        <v>17407.30173022235</v>
       </c>
       <c r="E87">
-        <v>9202.809999999998</v>
+        <v>9432.595999999998</v>
       </c>
       <c r="F87">
-        <v>19531.81</v>
+        <v>19761.596</v>
       </c>
       <c r="G87">
         <v>6462.2</v>
@@ -8427,28 +8427,28 @@
         <v>4301.8</v>
       </c>
       <c r="M87">
-        <v>1080.109093</v>
+        <v>1092.8162588</v>
       </c>
       <c r="N87">
-        <v>3221.690907</v>
+        <v>3208.9837412</v>
       </c>
       <c r="O87">
-        <v>773.20581768</v>
+        <v>770.156097888</v>
       </c>
       <c r="P87">
-        <v>2448.48508932</v>
+        <v>2438.827643312</v>
       </c>
       <c r="Q87">
-        <v>5338.28508932</v>
+        <v>5328.627643312</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2870970242557411</v>
+        <v>0.303553030935063</v>
       </c>
       <c r="T87">
-        <v>4.961320788216486</v>
+        <v>5.299673605790473</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.982745842877559</v>
+        <v>3.936434844704563</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07864150433090883</v>
+        <v>0.07849465502345648</v>
       </c>
       <c r="C88">
-        <v>4107.905730222352</v>
+        <v>3900.443744335174</v>
       </c>
       <c r="D88">
-        <v>17407.30173022235</v>
+        <v>17429.62574433517</v>
       </c>
       <c r="E88">
-        <v>9432.595999999998</v>
+        <v>9662.381999999998</v>
       </c>
       <c r="F88">
-        <v>19761.596</v>
+        <v>19991.382</v>
       </c>
       <c r="G88">
         <v>6462.2</v>
@@ -8509,28 +8509,28 @@
         <v>4301.8</v>
       </c>
       <c r="M88">
-        <v>1092.8162588</v>
+        <v>1105.5234246</v>
       </c>
       <c r="N88">
-        <v>3208.9837412</v>
+        <v>3196.2765754</v>
       </c>
       <c r="O88">
-        <v>770.156097888</v>
+        <v>767.1063780960001</v>
       </c>
       <c r="P88">
-        <v>2438.827643312</v>
+        <v>2429.170197304</v>
       </c>
       <c r="Q88">
-        <v>5328.627643312</v>
+        <v>5318.970197304</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.303553030935063</v>
+        <v>0.3225407309496652</v>
       </c>
       <c r="T88">
-        <v>5.299673605790473</v>
+        <v>5.69008070299123</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.936434844704563</v>
+        <v>3.891188467179224</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07849465502345648</v>
+        <v>0.07834780571600414</v>
       </c>
       <c r="C89">
-        <v>3900.443744335174</v>
+        <v>3693.039090889171</v>
       </c>
       <c r="D89">
-        <v>17429.62574433517</v>
+        <v>17452.00709088917</v>
       </c>
       <c r="E89">
-        <v>9662.381999999998</v>
+        <v>9892.167999999998</v>
       </c>
       <c r="F89">
-        <v>19991.382</v>
+        <v>20221.168</v>
       </c>
       <c r="G89">
         <v>6462.2</v>
@@ -8591,28 +8591,28 @@
         <v>4301.8</v>
       </c>
       <c r="M89">
-        <v>1105.5234246</v>
+        <v>1118.2305904</v>
       </c>
       <c r="N89">
-        <v>3196.2765754</v>
+        <v>3183.5694096</v>
       </c>
       <c r="O89">
-        <v>767.1063780960001</v>
+        <v>764.0566583040001</v>
       </c>
       <c r="P89">
-        <v>2429.170197304</v>
+        <v>2419.512751296</v>
       </c>
       <c r="Q89">
-        <v>5318.970197304</v>
+        <v>5309.312751296</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3225407309496652</v>
+        <v>0.3446930476333678</v>
       </c>
       <c r="T89">
-        <v>5.69008070299123</v>
+        <v>6.145555649725446</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.891188467179224</v>
+        <v>3.846970416415823</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07834780571600414</v>
+        <v>0.07820095640855179</v>
       </c>
       <c r="C90">
-        <v>3693.039090889171</v>
+        <v>3485.691991029722</v>
       </c>
       <c r="D90">
-        <v>17452.00709088917</v>
+        <v>17474.44599102972</v>
       </c>
       <c r="E90">
-        <v>9892.167999999998</v>
+        <v>10121.954</v>
       </c>
       <c r="F90">
-        <v>20221.168</v>
+        <v>20450.954</v>
       </c>
       <c r="G90">
         <v>6462.2</v>
@@ -8673,28 +8673,28 @@
         <v>4301.8</v>
       </c>
       <c r="M90">
-        <v>1118.2305904</v>
+        <v>1130.9377562</v>
       </c>
       <c r="N90">
-        <v>3183.5694096</v>
+        <v>3170.8622438</v>
       </c>
       <c r="O90">
-        <v>764.0566583040001</v>
+        <v>761.006938512</v>
       </c>
       <c r="P90">
-        <v>2419.512751296</v>
+        <v>2409.855305288</v>
       </c>
       <c r="Q90">
-        <v>5309.312751296</v>
+        <v>5299.655305288001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3446930476333678</v>
+        <v>0.3708730582595617</v>
       </c>
       <c r="T90">
-        <v>6.145555649725446</v>
+        <v>6.683844223138609</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.846970416415823</v>
+        <v>3.803746029714522</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07820095640855179</v>
+        <v>0.07805410710109945</v>
       </c>
       <c r="C91">
-        <v>3485.691991029722</v>
+        <v>3278.40266704102</v>
       </c>
       <c r="D91">
-        <v>17474.44599102972</v>
+        <v>17496.94266704102</v>
       </c>
       <c r="E91">
-        <v>10121.954</v>
+        <v>10351.74</v>
       </c>
       <c r="F91">
-        <v>20450.954</v>
+        <v>20680.74</v>
       </c>
       <c r="G91">
         <v>6462.2</v>
@@ -8755,28 +8755,28 @@
         <v>4301.8</v>
       </c>
       <c r="M91">
-        <v>1130.9377562</v>
+        <v>1143.644922</v>
       </c>
       <c r="N91">
-        <v>3170.8622438</v>
+        <v>3158.155078</v>
       </c>
       <c r="O91">
-        <v>761.006938512</v>
+        <v>757.95721872</v>
       </c>
       <c r="P91">
-        <v>2409.855305288</v>
+        <v>2400.19785928</v>
       </c>
       <c r="Q91">
-        <v>5299.655305288001</v>
+        <v>5289.99785928</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3708730582595617</v>
+        <v>0.4022890710109945</v>
       </c>
       <c r="T91">
-        <v>6.683844223138609</v>
+        <v>7.329790511234407</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.803746029714522</v>
+        <v>3.761482184939917</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07805410710109945</v>
+        <v>0.0779072577936471</v>
       </c>
       <c r="C92">
-        <v>3278.40266704102</v>
+        <v>3071.171342353427</v>
       </c>
       <c r="D92">
-        <v>17496.94266704102</v>
+        <v>17519.49734235342</v>
       </c>
       <c r="E92">
-        <v>10351.74</v>
+        <v>10581.526</v>
       </c>
       <c r="F92">
-        <v>20680.74</v>
+        <v>20910.526</v>
       </c>
       <c r="G92">
         <v>6462.2</v>
@@ -8837,28 +8837,28 @@
         <v>4301.8</v>
       </c>
       <c r="M92">
-        <v>1143.644922</v>
+        <v>1156.3520878</v>
       </c>
       <c r="N92">
-        <v>3158.155078</v>
+        <v>3145.4479122</v>
       </c>
       <c r="O92">
-        <v>757.95721872</v>
+        <v>754.907498928</v>
       </c>
       <c r="P92">
-        <v>2400.19785928</v>
+        <v>2390.540413272</v>
       </c>
       <c r="Q92">
-        <v>5289.99785928</v>
+        <v>5280.340413272001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4022890710109945</v>
+        <v>0.4406864199294123</v>
       </c>
       <c r="T92">
-        <v>7.329790511234407</v>
+        <v>8.119280418907048</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.761482184939917</v>
+        <v>3.720147215874643</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.0779072577936471</v>
+        <v>0.07776040848619475</v>
       </c>
       <c r="C93">
-        <v>3071.171342353427</v>
+        <v>2863.998241550831</v>
       </c>
       <c r="D93">
-        <v>17519.49734235342</v>
+        <v>17542.11024155083</v>
       </c>
       <c r="E93">
-        <v>10581.526</v>
+        <v>10811.312</v>
       </c>
       <c r="F93">
-        <v>20910.526</v>
+        <v>21140.312</v>
       </c>
       <c r="G93">
         <v>6462.2</v>
@@ -8919,28 +8919,28 @@
         <v>4301.8</v>
       </c>
       <c r="M93">
-        <v>1156.3520878</v>
+        <v>1169.0592536</v>
       </c>
       <c r="N93">
-        <v>3145.4479122</v>
+        <v>3132.7407464</v>
       </c>
       <c r="O93">
-        <v>754.907498928</v>
+        <v>751.8577791360001</v>
       </c>
       <c r="P93">
-        <v>2390.540413272</v>
+        <v>2380.882967264</v>
       </c>
       <c r="Q93">
-        <v>5280.340413272001</v>
+        <v>5270.682967264001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4406864199294123</v>
+        <v>0.4886831060774346</v>
       </c>
       <c r="T93">
-        <v>8.119280418907048</v>
+        <v>9.106142803497852</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.720147215874643</v>
+        <v>3.679710833093397</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07776040848619475</v>
+        <v>0.07761355917874239</v>
       </c>
       <c r="C94">
-        <v>2863.998241550831</v>
+        <v>2656.883590378144</v>
       </c>
       <c r="D94">
-        <v>17542.11024155083</v>
+        <v>17564.78159037814</v>
       </c>
       <c r="E94">
-        <v>10811.312</v>
+        <v>11041.098</v>
       </c>
       <c r="F94">
-        <v>21140.312</v>
+        <v>21370.098</v>
       </c>
       <c r="G94">
         <v>6462.2</v>
@@ -9001,28 +9001,28 @@
         <v>4301.8</v>
       </c>
       <c r="M94">
-        <v>1169.0592536</v>
+        <v>1181.7664194</v>
       </c>
       <c r="N94">
-        <v>3132.7407464</v>
+        <v>3120.0335806</v>
       </c>
       <c r="O94">
-        <v>751.8577791360001</v>
+        <v>748.8080593440001</v>
       </c>
       <c r="P94">
-        <v>2380.882967264</v>
+        <v>2371.225521256</v>
       </c>
       <c r="Q94">
-        <v>5270.682967264001</v>
+        <v>5261.025521256001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4886831060774346</v>
+        <v>0.5503931311248917</v>
       </c>
       <c r="T94">
-        <v>9.106142803497852</v>
+        <v>10.37496586940031</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.679710833093397</v>
+        <v>3.640144049941855</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07761355917874239</v>
+        <v>0.07746670987129006</v>
       </c>
       <c r="C95">
-        <v>2656.883590378144</v>
+        <v>2449.827615748782</v>
       </c>
       <c r="D95">
-        <v>17564.78159037814</v>
+        <v>17587.51161574878</v>
       </c>
       <c r="E95">
-        <v>11041.098</v>
+        <v>11270.884</v>
       </c>
       <c r="F95">
-        <v>21370.098</v>
+        <v>21599.884</v>
       </c>
       <c r="G95">
         <v>6462.2</v>
@@ -9083,28 +9083,28 @@
         <v>4301.8</v>
       </c>
       <c r="M95">
-        <v>1181.7664194</v>
+        <v>1194.4735852</v>
       </c>
       <c r="N95">
-        <v>3120.0335806</v>
+        <v>3107.3264148</v>
       </c>
       <c r="O95">
-        <v>748.8080593440001</v>
+        <v>745.7583395520001</v>
       </c>
       <c r="P95">
-        <v>2371.225521256</v>
+        <v>2361.568075248</v>
       </c>
       <c r="Q95">
-        <v>5261.025521256001</v>
+        <v>5251.368075248</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5503931311248917</v>
+        <v>0.6326731645215015</v>
       </c>
       <c r="T95">
-        <v>10.37496586940031</v>
+        <v>12.06672995727026</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.640144049941855</v>
+        <v>3.601419113240346</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07746670987129006</v>
+        <v>0.07731986056383772</v>
       </c>
       <c r="C96">
-        <v>2449.827615748782</v>
+        <v>2242.830545752258</v>
       </c>
       <c r="D96">
-        <v>17587.51161574878</v>
+        <v>17610.30054575226</v>
       </c>
       <c r="E96">
-        <v>11270.884</v>
+        <v>11500.67</v>
       </c>
       <c r="F96">
-        <v>21599.884</v>
+        <v>21829.67</v>
       </c>
       <c r="G96">
         <v>6462.2</v>
@@ -9165,28 +9165,28 @@
         <v>4301.8</v>
       </c>
       <c r="M96">
-        <v>1194.4735852</v>
+        <v>1207.180751</v>
       </c>
       <c r="N96">
-        <v>3107.3264148</v>
+        <v>3094.619249</v>
       </c>
       <c r="O96">
-        <v>745.7583395520001</v>
+        <v>742.70861976</v>
       </c>
       <c r="P96">
-        <v>2361.568075248</v>
+        <v>2351.91062924</v>
       </c>
       <c r="Q96">
-        <v>5251.368075248</v>
+        <v>5241.71062924</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6326731645215015</v>
+        <v>0.7478652112767553</v>
       </c>
       <c r="T96">
-        <v>12.06672995727026</v>
+        <v>14.43519968028819</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.601419113240346</v>
+        <v>3.563509438364131</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07731986056383772</v>
+        <v>0.07717301125638537</v>
       </c>
       <c r="C97">
-        <v>2242.830545752258</v>
+        <v>2035.892609661805</v>
       </c>
       <c r="D97">
-        <v>17610.30054575226</v>
+        <v>17633.14860966181</v>
       </c>
       <c r="E97">
-        <v>11500.67</v>
+        <v>11730.456</v>
       </c>
       <c r="F97">
-        <v>21829.67</v>
+        <v>22059.456</v>
       </c>
       <c r="G97">
         <v>6462.2</v>
@@ -9247,28 +9247,28 @@
         <v>4301.8</v>
       </c>
       <c r="M97">
-        <v>1207.180751</v>
+        <v>1219.8879168</v>
       </c>
       <c r="N97">
-        <v>3094.619249</v>
+        <v>3081.9120832</v>
       </c>
       <c r="O97">
-        <v>742.70861976</v>
+        <v>739.6588999679999</v>
       </c>
       <c r="P97">
-        <v>2351.91062924</v>
+        <v>2342.253183232</v>
       </c>
       <c r="Q97">
-        <v>5241.71062924</v>
+        <v>5232.053183232</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7478652112767553</v>
+        <v>0.9206532814096358</v>
       </c>
       <c r="T97">
-        <v>14.43519968028819</v>
+        <v>17.98790426481508</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.563509438364131</v>
+        <v>3.526389548381171</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07717301125638537</v>
+        <v>0.07702616194893303</v>
       </c>
       <c r="C98">
-        <v>2035.892609661809</v>
+        <v>1829.014037942059</v>
       </c>
       <c r="D98">
-        <v>17633.14860966181</v>
+        <v>17656.05603794206</v>
       </c>
       <c r="E98">
-        <v>11730.456</v>
+        <v>11960.242</v>
       </c>
       <c r="F98">
-        <v>22059.456</v>
+        <v>22289.242</v>
       </c>
       <c r="G98">
         <v>6462.2</v>
@@ -9329,28 +9329,28 @@
         <v>4301.8</v>
       </c>
       <c r="M98">
-        <v>1219.8879168</v>
+        <v>1232.5950826</v>
       </c>
       <c r="N98">
-        <v>3081.9120832</v>
+        <v>3069.2049174</v>
       </c>
       <c r="O98">
-        <v>739.658899968</v>
+        <v>736.6091801760001</v>
       </c>
       <c r="P98">
-        <v>2342.253183232</v>
+        <v>2332.595737224</v>
       </c>
       <c r="Q98">
-        <v>5232.053183232</v>
+        <v>5222.395737224</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9206532814096335</v>
+        <v>1.208633398297767</v>
       </c>
       <c r="T98">
-        <v>17.98790426481503</v>
+        <v>23.90907857235983</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.526389548381172</v>
+        <v>3.490035016954562</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.07702616194893303</v>
+        <v>0.07687931264148068</v>
       </c>
       <c r="C99">
-        <v>1829.014037942059</v>
+        <v>1622.195062256804</v>
       </c>
       <c r="D99">
-        <v>17656.05603794206</v>
+        <v>17679.0230622568</v>
       </c>
       <c r="E99">
-        <v>11960.242</v>
+        <v>12190.028</v>
       </c>
       <c r="F99">
-        <v>22289.242</v>
+        <v>22519.028</v>
       </c>
       <c r="G99">
         <v>6462.2</v>
@@ -9411,28 +9411,28 @@
         <v>4301.8</v>
       </c>
       <c r="M99">
-        <v>1232.5950826</v>
+        <v>1245.3022484</v>
       </c>
       <c r="N99">
-        <v>3069.2049174</v>
+        <v>3056.4977516</v>
       </c>
       <c r="O99">
-        <v>736.6091801760001</v>
+        <v>733.559460384</v>
       </c>
       <c r="P99">
-        <v>2332.595737224</v>
+        <v>2322.938291216</v>
       </c>
       <c r="Q99">
-        <v>5222.395737224</v>
+        <v>5212.738291216</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.208633398297767</v>
+        <v>1.784593632074032</v>
       </c>
       <c r="T99">
-        <v>23.90907857235983</v>
+        <v>35.75142718744942</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.490035016954562</v>
+        <v>3.454422414740739</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07687931264148068</v>
+        <v>0.07673246333402833</v>
       </c>
       <c r="C100">
-        <v>1622.195062256804</v>
+        <v>1415.435915476788</v>
       </c>
       <c r="D100">
-        <v>17679.0230622568</v>
+        <v>17702.04991547679</v>
       </c>
       <c r="E100">
-        <v>12190.028</v>
+        <v>12419.814</v>
       </c>
       <c r="F100">
-        <v>22519.028</v>
+        <v>22748.814</v>
       </c>
       <c r="G100">
         <v>6462.2</v>
@@ -9493,28 +9493,28 @@
         <v>4301.8</v>
       </c>
       <c r="M100">
-        <v>1245.3022484</v>
+        <v>1258.0094142</v>
       </c>
       <c r="N100">
-        <v>3056.4977516</v>
+        <v>3043.7905858</v>
       </c>
       <c r="O100">
-        <v>733.559460384</v>
+        <v>730.5097405920001</v>
       </c>
       <c r="P100">
-        <v>2322.938291216</v>
+        <v>2313.280845208</v>
       </c>
       <c r="Q100">
-        <v>5212.738291216</v>
+        <v>5203.080845208</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.784593632074032</v>
+        <v>3.51247433340283</v>
       </c>
       <c r="T100">
-        <v>35.75142718744942</v>
+        <v>71.2784730327182</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.454422414740739</v>
+        <v>3.419529259036288</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07673246333402833</v>
-      </c>
-      <c r="C101">
-        <v>1415.435915476788</v>
-      </c>
-      <c r="D101">
-        <v>17702.04991547679</v>
-      </c>
-      <c r="E101">
-        <v>12419.814</v>
-      </c>
-      <c r="F101">
-        <v>22748.814</v>
-      </c>
-      <c r="G101">
-        <v>6462.2</v>
-      </c>
-      <c r="H101">
-        <v>12649.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>7191.6</v>
-      </c>
-      <c r="K101">
-        <v>2889.8</v>
-      </c>
-      <c r="L101">
-        <v>4301.8</v>
-      </c>
-      <c r="M101">
-        <v>1258.0094142</v>
-      </c>
-      <c r="N101">
-        <v>3043.7905858</v>
-      </c>
-      <c r="O101">
-        <v>730.5097405920001</v>
-      </c>
-      <c r="P101">
-        <v>2313.280845208</v>
-      </c>
-      <c r="Q101">
-        <v>5203.080845208</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.51247433340283</v>
-      </c>
-      <c r="T101">
-        <v>71.2784730327182</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.24</v>
-      </c>
-      <c r="W101">
-        <v>0.042028</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.419529259036288</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
